--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8AE60F-4D8D-4DBB-B1B2-58839A6D59E4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAE88D7-8F21-4D68-9198-63E798EB6D3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -260,10 +260,10 @@
     <t>166-562-025-0000</t>
   </si>
   <si>
-    <t>05/16/2026</t>
-  </si>
-  <si>
     <t>JUNE 2026</t>
+  </si>
+  <si>
+    <t>06/16/2026</t>
   </si>
 </sst>
 </file>
@@ -2293,7 +2293,7 @@
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
       <c r="F3" s="45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -2375,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
@@ -2385,26 +2385,26 @@
         <v>70</v>
       </c>
       <c r="G7" s="20">
-        <v>518642084</v>
+        <v>518733994</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I7" s="21">
-        <f>1261704-123701.1</f>
-        <v>1138002.8999999999</v>
+        <f>1315032-273031.68</f>
+        <v>1042000.3200000001</v>
       </c>
       <c r="K7" s="21">
         <f>M7*12</f>
-        <v>121928.88214285714</v>
+        <v>111642.89142857144</v>
       </c>
       <c r="L7" s="27">
         <f>I7-K7</f>
-        <v>1016074.0178571427</v>
+        <v>930357.42857142864</v>
       </c>
       <c r="M7" s="33">
         <f>I7/112</f>
-        <v>10160.740178571428</v>
+        <v>9303.5742857142868</v>
       </c>
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
@@ -3137,20 +3137,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>1138002.8999999999</v>
+        <v>1042000.3200000001</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>121928.88214285714</v>
+        <v>111642.89142857144</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>1016074.0178571427</v>
+        <v>930357.42857142864</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>10160.740178571428</v>
+        <v>9303.5742857142868</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -3189,7 +3189,7 @@
       <c r="D36" s="44"/>
       <c r="E36" s="44"/>
       <c r="F36" s="45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAE88D7-8F21-4D68-9198-63E798EB6D3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B80904-C27E-4D1B-9802-326EC7EFA71B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B80904-C27E-4D1B-9802-326EC7EFA71B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC19795F-C147-4995-8FC7-89DB58BEEFC5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="78">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>06/16/2026</t>
+  </si>
+  <si>
+    <t>06/18/2026</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2421,9 @@
         <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="20" t="s">
         <v>68</v>
       </c>
@@ -2426,22 +2431,27 @@
       <c r="F8" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="20">
+        <v>518741040</v>
+      </c>
       <c r="H8" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="21">
+        <f>1412471-61256.62</f>
+        <v>1351214.38</v>
+      </c>
       <c r="K8" s="21">
         <f>M8*12</f>
-        <v>0</v>
+        <v>144772.96928571427</v>
       </c>
       <c r="L8" s="27">
         <f>I8-K8</f>
-        <v>0</v>
+        <v>1206441.4107142857</v>
       </c>
       <c r="M8" s="33">
         <f t="shared" ref="M8:M26" si="0">I8/112</f>
-        <v>0</v>
+        <v>12064.414107142857</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -3137,20 +3147,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>1042000.3200000001</v>
+        <v>2393214.7000000002</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>111642.89142857144</v>
+        <v>256415.86071428569</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>930357.42857142864</v>
+        <v>2136798.8392857146</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>9303.5742857142868</v>
+        <v>21367.988392857143</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC19795F-C147-4995-8FC7-89DB58BEEFC5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDD7DA3-2954-4E2A-B04A-F13B835476F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="420" windowWidth="29040" windowHeight="15900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="79">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>06/18/2026</t>
+  </si>
+  <si>
+    <t>06/19/2026</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2466,9 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
       </c>
@@ -2471,22 +2476,27 @@
       <c r="F9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>518745098</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="21"/>
+      <c r="I9" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K9" s="21">
         <f t="shared" ref="K9:K26" si="2">M9*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L9" s="27">
         <f t="shared" ref="L9:L26" si="3">I9-K9</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -3147,20 +3157,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>2393214.7000000002</v>
+        <v>3729565.66</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>256415.86071428569</v>
+        <v>399596.32071428571</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>2136798.8392857146</v>
+        <v>3329969.3392857146</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>21367.988392857143</v>
+        <v>33299.693392857145</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDD7DA3-2954-4E2A-B04A-F13B835476F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FCFB00-7B70-4E18-89D0-94AE4D022715}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="420" windowWidth="29040" windowHeight="15900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="80">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>06/19/2026</t>
+  </si>
+  <si>
+    <t>06/23/2026</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2511,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
       </c>
@@ -2516,22 +2521,27 @@
       <c r="F10" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20">
+        <v>518756120</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="21">
+        <f>1346606-57095.42</f>
+        <v>1289510.58</v>
+      </c>
       <c r="K10" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>138161.84785714286</v>
       </c>
       <c r="L10" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1151348.7321428573</v>
       </c>
       <c r="M10" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11513.487321428573</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -3157,20 +3167,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>3729565.66</v>
+        <v>5019076.24</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>399596.32071428571</v>
+        <v>537758.16857142863</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>3329969.3392857146</v>
+        <v>4481318.0714285718</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>33299.693392857145</v>
+        <v>44813.180714285714</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FCFB00-7B70-4E18-89D0-94AE4D022715}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10E8FC3-D6F0-4BCD-BA97-C60C1027F154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="105">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -273,6 +273,81 @@
   </si>
   <si>
     <t>06/23/2026</t>
+  </si>
+  <si>
+    <t>06/24/2026</t>
+  </si>
+  <si>
+    <t>MONTHLY PURCHASES</t>
+  </si>
+  <si>
+    <t>MONTHLY PURCHASES BEER EMPTIES</t>
+  </si>
+  <si>
+    <t>MONTHLY PURCHASES NAB EMPTIES</t>
+  </si>
+  <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>R03</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>R06</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>06/13/2026</t>
+  </si>
+  <si>
+    <t>R08</t>
+  </si>
+  <si>
+    <t>06/15/2026</t>
+  </si>
+  <si>
+    <t>R09</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>06/20/2026</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>MONTHLY PURCHASES SMB LILOY WW</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>TOTAL AMOUNT</t>
   </si>
 </sst>
 </file>
@@ -462,7 +537,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -524,9 +599,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -535,17 +607,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2250,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{423D5057-7111-4BE4-94EA-57775A7107A8}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
@@ -2259,22 +2330,22 @@
     <col min="4" max="4" width="30.28515625" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="68.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="38" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
     <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="14" style="36" customWidth="1"/>
+    <col min="13" max="13" width="14" style="35" customWidth="1"/>
     <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -2296,12 +2367,12 @@
       <c r="M2" s="29"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="43" t="s">
         <v>75</v>
       </c>
       <c r="G3" s="1"/>
@@ -2553,7 +2624,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
@@ -2561,22 +2634,27 @@
       <c r="F11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20">
+        <v>518760128</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K11" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L11" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M11" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2588,7 +2666,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
       </c>
@@ -2596,22 +2676,27 @@
       <c r="F12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20">
+        <v>518759920</v>
+      </c>
       <c r="H12" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K12" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L12" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M12" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2670,7 +2755,7 @@
       <c r="H14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="37"/>
+      <c r="I14" s="36"/>
       <c r="K14" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3141,384 +3226,668 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G28"/>
-      <c r="M28" s="34"/>
+      <c r="I28" s="44">
+        <f>SUM(I7:I27)</f>
+        <v>7691778.1600000001</v>
+      </c>
+      <c r="J28" s="44">
+        <f ca="1">SUM(J7:J31)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="44">
+        <f>SUM(K7:K27)</f>
+        <v>824119.08857142855</v>
+      </c>
+      <c r="L28" s="44">
+        <f>SUM(L7:L27)</f>
+        <v>6867659.0714285718</v>
+      </c>
+      <c r="M28" s="44">
+        <f>SUM(M7:M27)</f>
+        <v>68676.590714285718</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G29"/>
       <c r="M29" s="34"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G30"/>
-      <c r="M30" s="34"/>
+    <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C30" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="28"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="24"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="35"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="30"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G32"/>
-      <c r="I32" s="46">
-        <f>SUM(I7:I31)</f>
-        <v>5019076.24</v>
-      </c>
-      <c r="J32" s="47"/>
-      <c r="K32" s="46">
-        <f>SUM(K7:K31)</f>
-        <v>537758.16857142863</v>
-      </c>
-      <c r="L32" s="46">
-        <f>SUM(L7:L31)</f>
-        <v>4481318.0714285718</v>
-      </c>
-      <c r="M32" s="48">
-        <f>SUM(M7:M31)</f>
-        <v>44813.180714285714</v>
-      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="31"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G33"/>
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="M33" s="32">
+        <v>2307</v>
+      </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C34" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="28"/>
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="C34" s="19">
+        <v>46028</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I34" s="21">
+        <v>105480</v>
+      </c>
+      <c r="K34" s="21">
+        <f t="shared" ref="K34:K53" si="7">M34*12</f>
+        <v>11301.428571428572</v>
+      </c>
+      <c r="L34" s="27">
+        <f>I34-K34</f>
+        <v>94178.57142857142</v>
+      </c>
+      <c r="M34" s="33">
+        <f t="shared" ref="M34:M53" si="8">I34/112</f>
+        <v>941.78571428571433</v>
+      </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="29"/>
-    </row>
-    <row r="36" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C36" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="28"/>
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="C35" s="19">
+        <v>46240</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" s="21">
+        <v>199368</v>
+      </c>
+      <c r="K35" s="21">
+        <f t="shared" si="7"/>
+        <v>21360.857142857145</v>
+      </c>
+      <c r="L35" s="27">
+        <f t="shared" ref="L35:L53" si="9">I35-K35</f>
+        <v>178007.14285714284</v>
+      </c>
+      <c r="M35" s="33">
+        <f t="shared" si="8"/>
+        <v>1780.0714285714287</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>4</v>
+      </c>
+      <c r="C36" s="19">
+        <v>46271</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I36" s="21">
+        <v>177156</v>
+      </c>
+      <c r="K36" s="21">
+        <f t="shared" si="7"/>
+        <v>18981</v>
+      </c>
+      <c r="L36" s="27">
+        <f t="shared" si="9"/>
+        <v>158175</v>
+      </c>
+      <c r="M36" s="33">
+        <f t="shared" si="8"/>
+        <v>1581.75</v>
+      </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="30"/>
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="C37" s="19">
+        <v>46301</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I37" s="21">
+        <v>203796</v>
+      </c>
+      <c r="K37" s="21">
+        <f t="shared" si="7"/>
+        <v>21835.285714285714</v>
+      </c>
+      <c r="L37" s="27">
+        <f t="shared" si="9"/>
+        <v>181960.71428571429</v>
+      </c>
+      <c r="M37" s="33">
+        <f t="shared" si="8"/>
+        <v>1819.6071428571429</v>
+      </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M38" s="31"/>
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="C38" s="19">
+        <v>46332</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I38" s="21">
+        <v>187884</v>
+      </c>
+      <c r="K38" s="21">
+        <f t="shared" si="7"/>
+        <v>20130.428571428572</v>
+      </c>
+      <c r="L38" s="27">
+        <f t="shared" si="9"/>
+        <v>167753.57142857142</v>
+      </c>
+      <c r="M38" s="33">
+        <f t="shared" si="8"/>
+        <v>1677.5357142857142</v>
+      </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="9" t="s">
+      <c r="A39">
         <v>7</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="M39" s="32">
-        <v>2307</v>
+      <c r="C39" s="19">
+        <v>46332</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I39" s="21">
+        <v>191808</v>
+      </c>
+      <c r="K39" s="21">
+        <f t="shared" si="7"/>
+        <v>20550.857142857145</v>
+      </c>
+      <c r="L39" s="27">
+        <f t="shared" si="9"/>
+        <v>171257.14285714284</v>
+      </c>
+      <c r="M39" s="33">
+        <f t="shared" si="8"/>
+        <v>1712.5714285714287</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>2</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
+        <v>8</v>
+      </c>
+      <c r="C40" s="19">
+        <v>46362</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40" s="21">
+        <v>203796</v>
+      </c>
       <c r="K40" s="21">
-        <f t="shared" ref="K40:K59" si="7">M40*12</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>21835.285714285714</v>
       </c>
       <c r="L40" s="27">
-        <f>I40-K40</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>181960.71428571429</v>
       </c>
       <c r="M40" s="33">
-        <f t="shared" ref="M40:M59" si="8">I40/112</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>3</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="20"/>
+        <v>9</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21"/>
+      <c r="F41" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I41" s="21">
+        <v>190800</v>
+      </c>
       <c r="K41" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20442.857142857145</v>
       </c>
       <c r="L41" s="27">
-        <f t="shared" ref="L41:L59" si="9">I41-K41</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>170357.14285714284</v>
       </c>
       <c r="M41" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1703.5714285714287</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>4</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="21"/>
+      <c r="F42" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42" s="21">
+        <v>149328</v>
+      </c>
       <c r="K42" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15999.428571428571</v>
       </c>
       <c r="L42" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>133328.57142857142</v>
       </c>
       <c r="M42" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1333.2857142857142</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>5</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="20"/>
+        <v>11</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="21"/>
+      <c r="F43" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I43" s="21">
+        <v>163404</v>
+      </c>
       <c r="K43" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17507.571428571428</v>
       </c>
       <c r="L43" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>145896.42857142858</v>
       </c>
       <c r="M43" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1458.9642857142858</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>6</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="21"/>
+      <c r="F44" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G44" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I44" s="21">
+        <v>191808</v>
+      </c>
       <c r="K44" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20550.857142857145</v>
       </c>
       <c r="L44" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>171257.14285714284</v>
       </c>
       <c r="M44" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1712.5714285714287</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>7</v>
-      </c>
-      <c r="C45" s="19"/>
-      <c r="D45" s="20"/>
+        <v>13</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="21"/>
+      <c r="F45" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G45" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="21">
+        <v>204888</v>
+      </c>
       <c r="K45" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21952.285714285714</v>
       </c>
       <c r="L45" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>182935.71428571429</v>
       </c>
       <c r="M45" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1829.3571428571429</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>8</v>
-      </c>
-      <c r="C46" s="19"/>
-      <c r="D46" s="20"/>
+        <v>14</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="21"/>
+      <c r="F46" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I46" s="21">
+        <v>91656</v>
+      </c>
       <c r="K46" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9820.2857142857138</v>
       </c>
       <c r="L46" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>81835.71428571429</v>
       </c>
       <c r="M46" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>818.35714285714289</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>9</v>
-      </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="20"/>
+        <v>15</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="21"/>
+      <c r="F47" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="H47" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I47" s="21">
+        <v>203796</v>
+      </c>
       <c r="K47" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="L47" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="M47" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10</v>
-      </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="21"/>
+      <c r="F48" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G48" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I48" s="21">
+        <v>143856</v>
+      </c>
       <c r="K48" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15413.142857142855</v>
       </c>
       <c r="L48" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>128442.85714285714</v>
       </c>
       <c r="M48" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1284.4285714285713</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
+      <c r="D49" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="20"/>
+      <c r="F49" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G49" s="37"/>
+      <c r="H49" s="20" t="s">
+        <v>74</v>
+      </c>
       <c r="I49" s="21"/>
       <c r="K49" s="21">
         <f t="shared" si="7"/>
@@ -3535,14 +3904,20 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
+      <c r="D50" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="20"/>
+      <c r="F50" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G50" s="37"/>
+      <c r="H50" s="20" t="s">
+        <v>74</v>
+      </c>
       <c r="I50" s="21"/>
       <c r="K50" s="21">
         <f t="shared" si="7"/>
@@ -3559,14 +3934,20 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C51" s="19"/>
-      <c r="D51" s="20"/>
+      <c r="D51" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="20"/>
+      <c r="F51" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" s="37"/>
+      <c r="H51" s="20" t="s">
+        <v>74</v>
+      </c>
       <c r="I51" s="21"/>
       <c r="K51" s="21">
         <f t="shared" si="7"/>
@@ -3583,14 +3964,20 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C52" s="19"/>
-      <c r="D52" s="20"/>
+      <c r="D52" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="20"/>
+      <c r="F52" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" s="37"/>
+      <c r="H52" s="20" t="s">
+        <v>74</v>
+      </c>
       <c r="I52" s="21"/>
       <c r="K52" s="21">
         <f t="shared" si="7"/>
@@ -3607,14 +3994,20 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C53" s="19"/>
-      <c r="D53" s="20"/>
+      <c r="D53" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="20"/>
+      <c r="F53" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G53" s="37"/>
+      <c r="H53" s="20" t="s">
+        <v>74</v>
+      </c>
       <c r="I53" s="21"/>
       <c r="K53" s="21">
         <f t="shared" si="7"/>
@@ -3631,201 +4024,1625 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54">
+        <v>22</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G54" s="37"/>
+      <c r="H54" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="33"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I55" s="44">
+        <f>SUM(I34:I54)</f>
+        <v>2608824</v>
+      </c>
+      <c r="J55" s="44">
+        <f ca="1">SUM(J34:J58)</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="44">
+        <f>SUM(K34:K54)</f>
+        <v>279516.85714285716</v>
+      </c>
+      <c r="L55" s="44">
+        <f>SUM(L34:L54)</f>
+        <v>2329307.1428571427</v>
+      </c>
+      <c r="M55" s="45">
+        <f>SUM(M34:M54)</f>
+        <v>23293.071428571428</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M56" s="34"/>
+    </row>
+    <row r="57" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C57" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="28"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="30"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H59" s="9"/>
+      <c r="I59" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="31"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="M60" s="32">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2</v>
+      </c>
+      <c r="C61" s="19">
+        <v>46028</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" s="12"/>
+      <c r="F61" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G61" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I61" s="21">
+        <v>33804</v>
+      </c>
+      <c r="K61" s="21">
+        <f t="shared" ref="K61:K80" si="10">M61*12</f>
+        <v>3621.8571428571427</v>
+      </c>
+      <c r="L61" s="27">
+        <f>I61-K61</f>
+        <v>30182.142857142859</v>
+      </c>
+      <c r="M61" s="33">
+        <f t="shared" ref="M61:M80" si="11">I61/112</f>
+        <v>301.82142857142856</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="C62" s="19">
+        <v>46271</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G62" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I62" s="21">
+        <v>11340</v>
+      </c>
+      <c r="K62" s="21">
+        <f t="shared" si="10"/>
+        <v>1215</v>
+      </c>
+      <c r="L62" s="27">
+        <f t="shared" ref="L62:L80" si="12">I62-K62</f>
+        <v>10125</v>
+      </c>
+      <c r="M62" s="33">
+        <f t="shared" si="11"/>
+        <v>101.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>4</v>
+      </c>
+      <c r="C63" s="19">
+        <v>46332</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I63" s="21">
+        <v>5670</v>
+      </c>
+      <c r="K63" s="21">
+        <f t="shared" si="10"/>
+        <v>607.5</v>
+      </c>
+      <c r="L63" s="27">
+        <f t="shared" si="12"/>
+        <v>5062.5</v>
+      </c>
+      <c r="M63" s="33">
+        <f t="shared" si="11"/>
+        <v>50.625</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="C64" s="19">
+        <v>46332</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G64" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I64" s="21">
+        <v>5616</v>
+      </c>
+      <c r="K64" s="21">
+        <f t="shared" si="10"/>
+        <v>601.71428571428578</v>
+      </c>
+      <c r="L64" s="27">
+        <f t="shared" si="12"/>
+        <v>5014.2857142857138</v>
+      </c>
+      <c r="M64" s="33">
+        <f t="shared" si="11"/>
+        <v>50.142857142857146</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>6</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G65" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I65" s="21">
+        <v>11286</v>
+      </c>
+      <c r="K65" s="21">
+        <f t="shared" si="10"/>
+        <v>1209.2142857142858</v>
+      </c>
+      <c r="L65" s="27">
+        <f t="shared" si="12"/>
+        <v>10076.785714285714</v>
+      </c>
+      <c r="M65" s="33">
+        <f t="shared" si="11"/>
+        <v>100.76785714285714</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>7</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G66" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I66" s="21">
+        <v>5616</v>
+      </c>
+      <c r="K66" s="21">
+        <f t="shared" si="10"/>
+        <v>601.71428571428578</v>
+      </c>
+      <c r="L66" s="27">
+        <f t="shared" si="12"/>
+        <v>5014.2857142857138</v>
+      </c>
+      <c r="M66" s="33">
+        <f t="shared" si="11"/>
+        <v>50.142857142857146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>8</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G67" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I67" s="21">
+        <v>5616</v>
+      </c>
+      <c r="K67" s="21">
+        <f t="shared" si="10"/>
+        <v>601.71428571428578</v>
+      </c>
+      <c r="L67" s="27">
+        <f t="shared" si="12"/>
+        <v>5014.2857142857138</v>
+      </c>
+      <c r="M67" s="33">
+        <f t="shared" si="11"/>
+        <v>50.142857142857146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>9</v>
+      </c>
+      <c r="C68" s="19"/>
+      <c r="D68" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G68" s="37"/>
+      <c r="H68" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I68" s="21"/>
+      <c r="K68" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M68" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>10</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G69" s="37"/>
+      <c r="H69" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I69" s="21"/>
+      <c r="K69" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>11</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G70" s="37"/>
+      <c r="H70" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I70" s="21"/>
+      <c r="K70" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M70" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>12</v>
+      </c>
+      <c r="C71" s="19"/>
+      <c r="D71" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G71" s="37"/>
+      <c r="H71" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I71" s="21"/>
+      <c r="K71" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M71" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>13</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="D72" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G72" s="37"/>
+      <c r="H72" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I72" s="21"/>
+      <c r="K72" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>14</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G73" s="37"/>
+      <c r="H73" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I73" s="21"/>
+      <c r="K73" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L73" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>15</v>
+      </c>
+      <c r="C74" s="19"/>
+      <c r="D74" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G74" s="37"/>
+      <c r="H74" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I74" s="21"/>
+      <c r="K74" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L74" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M74" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>16</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="21"/>
-      <c r="K54" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L54" s="27">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M54" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="C75" s="19"/>
+      <c r="D75" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G75" s="37"/>
+      <c r="H75" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I75" s="21"/>
+      <c r="K75" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>17</v>
       </c>
-      <c r="C55" s="19"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="21"/>
-      <c r="K55" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L55" s="27">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M55" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56">
+      <c r="C76" s="19"/>
+      <c r="D76" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G76" s="37"/>
+      <c r="H76" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I76" s="21"/>
+      <c r="K76" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L76" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M76" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77">
         <v>18</v>
       </c>
-      <c r="C56" s="19"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="21"/>
-      <c r="K56" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L56" s="27">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M56" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="C77" s="19"/>
+      <c r="D77" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G77" s="37"/>
+      <c r="H77" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I77" s="21"/>
+      <c r="K77" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L77" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>19</v>
       </c>
-      <c r="C57" s="19"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="21"/>
-      <c r="K57" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L57" s="27">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58">
+      <c r="C78" s="19"/>
+      <c r="D78" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G78" s="37"/>
+      <c r="H78" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I78" s="21"/>
+      <c r="K78" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M78" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79">
         <v>20</v>
       </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="21"/>
-      <c r="K58" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="27">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="C79" s="19"/>
+      <c r="D79" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G79" s="37"/>
+      <c r="H79" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I79" s="21"/>
+      <c r="K79" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L79" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M79" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>21</v>
       </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="21"/>
-      <c r="K59" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L59" s="27">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60">
+      <c r="C80" s="19"/>
+      <c r="D80" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G80" s="37"/>
+      <c r="H80" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I80" s="21"/>
+      <c r="K80" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="33">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81">
         <v>22</v>
       </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="21"/>
-      <c r="K60" s="21"/>
-      <c r="L60" s="21"/>
-      <c r="M60" s="33"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M61" s="34"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M62" s="34"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M63" s="34"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="24"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="35"/>
-    </row>
-    <row r="65" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I65" s="46">
-        <f>SUM(I40:I64)</f>
-        <v>0</v>
-      </c>
-      <c r="J65" s="47"/>
-      <c r="K65" s="46">
-        <f>SUM(K40:K64)</f>
-        <v>0</v>
-      </c>
-      <c r="L65" s="46">
-        <f>SUM(L40:L64)</f>
-        <v>0</v>
-      </c>
-      <c r="M65" s="48">
-        <f>SUM(M40:M64)</f>
-        <v>0</v>
+      <c r="C81" s="19"/>
+      <c r="D81" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G81" s="37"/>
+      <c r="H81" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I81" s="21"/>
+      <c r="K81" s="21"/>
+      <c r="L81" s="21"/>
+      <c r="M81" s="33"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I82" s="44">
+        <f>SUM(I61:I81)</f>
+        <v>78948</v>
+      </c>
+      <c r="J82" s="44">
+        <f ca="1">SUM(J61:J85)</f>
+        <v>0</v>
+      </c>
+      <c r="K82" s="44">
+        <f>SUM(K61:K81)</f>
+        <v>8458.7142857142881</v>
+      </c>
+      <c r="L82" s="44">
+        <f>SUM(L61:L81)</f>
+        <v>70489.285714285696</v>
+      </c>
+      <c r="M82" s="45">
+        <f>SUM(M61:M81)</f>
+        <v>704.89285714285711</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C84" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84" s="42"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="28"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="30"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H86" s="9"/>
+      <c r="K86" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="L86" s="10"/>
+      <c r="M86" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N86" s="31"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>73</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I87" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N87" s="32">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E88" s="12"/>
+      <c r="F88" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G88" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="H88" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I88" s="21">
+        <v>1608</v>
+      </c>
+      <c r="J88" s="21"/>
+      <c r="K88" s="21">
+        <v>16488</v>
+      </c>
+      <c r="L88" s="21">
+        <f t="shared" ref="L88:L107" si="13">N88*12</f>
+        <v>1766.5714285714287</v>
+      </c>
+      <c r="M88" s="27">
+        <f>K88-L88</f>
+        <v>14721.428571428571</v>
+      </c>
+      <c r="N88" s="33">
+        <f>K88/112</f>
+        <v>147.21428571428572</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>3</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D89" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" s="37"/>
+      <c r="H89" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I89" s="21">
+        <v>1849</v>
+      </c>
+      <c r="J89" s="21"/>
+      <c r="K89" s="21">
+        <v>11328</v>
+      </c>
+      <c r="L89" s="21">
+        <f t="shared" si="13"/>
+        <v>1213.7142857142858</v>
+      </c>
+      <c r="M89" s="27">
+        <f>K89-L89</f>
+        <v>10114.285714285714</v>
+      </c>
+      <c r="N89" s="33">
+        <f>K89/112</f>
+        <v>101.14285714285714</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90" s="37"/>
+      <c r="H90" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I90" s="21">
+        <v>1836</v>
+      </c>
+      <c r="J90" s="21"/>
+      <c r="K90" s="21">
+        <v>11016</v>
+      </c>
+      <c r="L90" s="21">
+        <f t="shared" si="13"/>
+        <v>1180.2857142857142</v>
+      </c>
+      <c r="M90" s="27">
+        <f>K90-L90</f>
+        <v>9835.7142857142862</v>
+      </c>
+      <c r="N90" s="33">
+        <f>K90/112</f>
+        <v>98.357142857142861</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>5</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G91" s="37"/>
+      <c r="H91" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I91" s="21">
+        <v>1709</v>
+      </c>
+      <c r="J91" s="21"/>
+      <c r="K91" s="21">
+        <v>13800</v>
+      </c>
+      <c r="L91" s="21">
+        <f t="shared" si="13"/>
+        <v>1478.5714285714284</v>
+      </c>
+      <c r="M91" s="27">
+        <f>K91-L91</f>
+        <v>12321.428571428572</v>
+      </c>
+      <c r="N91" s="33">
+        <f>K91/112</f>
+        <v>123.21428571428571</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>6</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G92" s="37"/>
+      <c r="H92" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I92" s="21">
+        <v>1836</v>
+      </c>
+      <c r="J92" s="21"/>
+      <c r="K92" s="21">
+        <v>11016</v>
+      </c>
+      <c r="L92" s="21">
+        <f t="shared" si="13"/>
+        <v>1180.2857142857142</v>
+      </c>
+      <c r="M92" s="27">
+        <f>K92-L92</f>
+        <v>9835.7142857142862</v>
+      </c>
+      <c r="N92" s="33">
+        <f>K92/112</f>
+        <v>98.357142857142861</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>7</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G93" s="37"/>
+      <c r="H93" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93" s="21">
+        <v>1836</v>
+      </c>
+      <c r="J93" s="21"/>
+      <c r="K93" s="21">
+        <v>11016</v>
+      </c>
+      <c r="L93" s="21">
+        <f t="shared" si="13"/>
+        <v>1180.2857142857142</v>
+      </c>
+      <c r="M93" s="27">
+        <f>K93-L93</f>
+        <v>9835.7142857142862</v>
+      </c>
+      <c r="N93" s="33">
+        <f>K93/112</f>
+        <v>98.357142857142861</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>8</v>
+      </c>
+      <c r="C94" s="19"/>
+      <c r="D94" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E94" s="20"/>
+      <c r="F94" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" s="37"/>
+      <c r="H94" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I94" s="21"/>
+      <c r="J94" s="21"/>
+      <c r="K94" s="21"/>
+      <c r="L94" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="27">
+        <f>K94-L94</f>
+        <v>0</v>
+      </c>
+      <c r="N94" s="33">
+        <f>K94/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>9</v>
+      </c>
+      <c r="C95" s="19"/>
+      <c r="D95" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E95" s="20"/>
+      <c r="F95" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G95" s="37"/>
+      <c r="H95" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I95" s="21"/>
+      <c r="J95" s="21"/>
+      <c r="K95" s="21"/>
+      <c r="L95" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M95" s="27">
+        <f>K95-L95</f>
+        <v>0</v>
+      </c>
+      <c r="N95" s="33">
+        <f>K95/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>10</v>
+      </c>
+      <c r="C96" s="19"/>
+      <c r="D96" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G96" s="37"/>
+      <c r="H96" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I96" s="21"/>
+      <c r="J96" s="21"/>
+      <c r="K96" s="21"/>
+      <c r="L96" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M96" s="27">
+        <f>K96-L96</f>
+        <v>0</v>
+      </c>
+      <c r="N96" s="33">
+        <f>K96/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>11</v>
+      </c>
+      <c r="C97" s="19"/>
+      <c r="D97" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E97" s="20"/>
+      <c r="F97" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G97" s="37"/>
+      <c r="H97" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I97" s="21"/>
+      <c r="J97" s="21"/>
+      <c r="K97" s="21"/>
+      <c r="L97" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M97" s="27">
+        <f>K97-L97</f>
+        <v>0</v>
+      </c>
+      <c r="N97" s="33">
+        <f>K97/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>12</v>
+      </c>
+      <c r="C98" s="19"/>
+      <c r="D98" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E98" s="20"/>
+      <c r="F98" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G98" s="37"/>
+      <c r="H98" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I98" s="21"/>
+      <c r="J98" s="21"/>
+      <c r="K98" s="21"/>
+      <c r="L98" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="27">
+        <f>K98-L98</f>
+        <v>0</v>
+      </c>
+      <c r="N98" s="33">
+        <f>K98/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>13</v>
+      </c>
+      <c r="C99" s="19"/>
+      <c r="D99" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E99" s="20"/>
+      <c r="F99" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G99" s="37"/>
+      <c r="H99" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I99" s="21"/>
+      <c r="J99" s="21"/>
+      <c r="K99" s="21"/>
+      <c r="L99" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M99" s="27">
+        <f>K99-L99</f>
+        <v>0</v>
+      </c>
+      <c r="N99" s="33">
+        <f>K99/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>14</v>
+      </c>
+      <c r="C100" s="19"/>
+      <c r="D100" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E100" s="20"/>
+      <c r="F100" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G100" s="37"/>
+      <c r="H100" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I100" s="21"/>
+      <c r="J100" s="21"/>
+      <c r="K100" s="21"/>
+      <c r="L100" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M100" s="27">
+        <f>K100-L100</f>
+        <v>0</v>
+      </c>
+      <c r="N100" s="33">
+        <f>K100/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>15</v>
+      </c>
+      <c r="C101" s="19"/>
+      <c r="D101" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E101" s="20"/>
+      <c r="F101" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G101" s="37"/>
+      <c r="H101" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I101" s="21"/>
+      <c r="J101" s="21"/>
+      <c r="K101" s="21"/>
+      <c r="L101" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M101" s="27">
+        <f>K101-L101</f>
+        <v>0</v>
+      </c>
+      <c r="N101" s="33">
+        <f>K101/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>16</v>
+      </c>
+      <c r="C102" s="19"/>
+      <c r="D102" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" s="20"/>
+      <c r="F102" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G102" s="37"/>
+      <c r="H102" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I102" s="21"/>
+      <c r="J102" s="21"/>
+      <c r="K102" s="21"/>
+      <c r="L102" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M102" s="27">
+        <f>K102-L102</f>
+        <v>0</v>
+      </c>
+      <c r="N102" s="33">
+        <f>K102/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>17</v>
+      </c>
+      <c r="C103" s="19"/>
+      <c r="D103" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E103" s="20"/>
+      <c r="F103" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G103" s="37"/>
+      <c r="H103" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I103" s="21"/>
+      <c r="J103" s="21"/>
+      <c r="K103" s="21"/>
+      <c r="L103" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M103" s="27">
+        <f>K103-L103</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="33">
+        <f>K103/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>18</v>
+      </c>
+      <c r="C104" s="19"/>
+      <c r="D104" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E104" s="20"/>
+      <c r="F104" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G104" s="37"/>
+      <c r="H104" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104" s="21"/>
+      <c r="J104" s="21"/>
+      <c r="K104" s="21"/>
+      <c r="L104" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M104" s="27">
+        <f>K104-L104</f>
+        <v>0</v>
+      </c>
+      <c r="N104" s="33">
+        <f>K104/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>19</v>
+      </c>
+      <c r="C105" s="19"/>
+      <c r="D105" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E105" s="20"/>
+      <c r="F105" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G105" s="37"/>
+      <c r="H105" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I105" s="21"/>
+      <c r="J105" s="21"/>
+      <c r="K105" s="21"/>
+      <c r="L105" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="27">
+        <f>K105-L105</f>
+        <v>0</v>
+      </c>
+      <c r="N105" s="33">
+        <f>K105/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>20</v>
+      </c>
+      <c r="C106" s="19"/>
+      <c r="D106" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E106" s="20"/>
+      <c r="F106" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G106" s="37"/>
+      <c r="H106" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I106" s="21"/>
+      <c r="J106" s="21"/>
+      <c r="K106" s="21"/>
+      <c r="L106" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="27">
+        <f>K106-L106</f>
+        <v>0</v>
+      </c>
+      <c r="N106" s="33">
+        <f>K106/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>21</v>
+      </c>
+      <c r="C107" s="19"/>
+      <c r="D107" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E107" s="20"/>
+      <c r="F107" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G107" s="37"/>
+      <c r="H107" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I107" s="21"/>
+      <c r="J107" s="21"/>
+      <c r="K107" s="21"/>
+      <c r="L107" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="27">
+        <f>K107-L107</f>
+        <v>0</v>
+      </c>
+      <c r="N107" s="33">
+        <f>K107/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>22</v>
+      </c>
+      <c r="C108" s="19"/>
+      <c r="D108" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E108" s="20"/>
+      <c r="F108" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G108" s="37"/>
+      <c r="H108" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I108" s="21"/>
+      <c r="J108" s="21"/>
+      <c r="K108" s="21"/>
+      <c r="L108" s="21"/>
+      <c r="M108" s="21"/>
+      <c r="N108" s="33"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I109" s="44">
+        <f>SUM(I88:I108)</f>
+        <v>10674</v>
+      </c>
+      <c r="J109" s="44">
+        <f ca="1">SUM(J88:J112)</f>
+        <v>0</v>
+      </c>
+      <c r="K109" s="44">
+        <f>SUM(K88:K108)</f>
+        <v>74664</v>
+      </c>
+      <c r="L109" s="44">
+        <f>SUM(L88:L108)</f>
+        <v>7999.7142857142862</v>
+      </c>
+      <c r="M109" s="45">
+        <f>SUM(M88:M108)</f>
+        <v>66664.28571428571</v>
+      </c>
+      <c r="N109" s="45">
+        <f>SUM(N88:N108)</f>
+        <v>666.64285714285722</v>
       </c>
     </row>
   </sheetData>

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10E8FC3-D6F0-4BCD-BA97-C60C1027F154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47768989-1745-42BC-A69F-D410D09D3130}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="110">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -348,6 +348,21 @@
   </si>
   <si>
     <t>TOTAL AMOUNT</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
   </si>
 </sst>
 </file>
@@ -3334,7 +3349,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="19">
         <v>46028</v>
@@ -3370,7 +3385,8 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>3</v>
+        <f>A34+1</f>
+        <v>2</v>
       </c>
       <c r="C35" s="19">
         <v>46240</v>
@@ -3406,7 +3422,8 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>4</v>
+        <f t="shared" ref="A36:A54" si="10">A35+1</f>
+        <v>3</v>
       </c>
       <c r="C36" s="19">
         <v>46271</v>
@@ -3442,7 +3459,8 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="C37" s="19">
         <v>46301</v>
@@ -3478,7 +3496,8 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>6</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="C38" s="19">
         <v>46332</v>
@@ -3514,7 +3533,8 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>7</v>
+        <f t="shared" si="10"/>
+        <v>6</v>
       </c>
       <c r="C39" s="19">
         <v>46332</v>
@@ -3550,7 +3570,8 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="C40" s="19">
         <v>46362</v>
@@ -3586,7 +3607,8 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>9</v>
+        <f t="shared" si="10"/>
+        <v>8</v>
       </c>
       <c r="C41" s="19" t="s">
         <v>91</v>
@@ -3622,7 +3644,8 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>9</v>
       </c>
       <c r="C42" s="19" t="s">
         <v>93</v>
@@ -3658,7 +3681,8 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>11</v>
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="C43" s="19" t="s">
         <v>76</v>
@@ -3694,7 +3718,8 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>12</v>
+        <f t="shared" si="10"/>
+        <v>11</v>
       </c>
       <c r="C44" s="19" t="s">
         <v>77</v>
@@ -3730,7 +3755,8 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>13</v>
+        <f t="shared" si="10"/>
+        <v>12</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>78</v>
@@ -3766,7 +3792,8 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>14</v>
+        <f t="shared" si="10"/>
+        <v>13</v>
       </c>
       <c r="C46" s="19" t="s">
         <v>98</v>
@@ -3802,7 +3829,8 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>15</v>
+        <f t="shared" si="10"/>
+        <v>14</v>
       </c>
       <c r="C47" s="19" t="s">
         <v>79</v>
@@ -3838,7 +3866,8 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>16</v>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="C48" s="19" t="s">
         <v>80</v>
@@ -3874,7 +3903,8 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>17</v>
+        <f t="shared" si="10"/>
+        <v>16</v>
       </c>
       <c r="C49" s="19"/>
       <c r="D49" s="20" t="s">
@@ -3904,7 +3934,8 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>18</v>
+        <f t="shared" si="10"/>
+        <v>17</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="20" t="s">
@@ -3934,7 +3965,8 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>19</v>
+        <f t="shared" si="10"/>
+        <v>18</v>
       </c>
       <c r="C51" s="19"/>
       <c r="D51" s="20" t="s">
@@ -3964,7 +3996,8 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>20</v>
+        <f t="shared" si="10"/>
+        <v>19</v>
       </c>
       <c r="C52" s="19"/>
       <c r="D52" s="20" t="s">
@@ -3994,7 +4027,8 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>21</v>
+        <f t="shared" si="10"/>
+        <v>20</v>
       </c>
       <c r="C53" s="19"/>
       <c r="D53" s="20" t="s">
@@ -4024,7 +4058,8 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>22</v>
+        <f t="shared" si="10"/>
+        <v>21</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="20" t="s">
@@ -4151,7 +4186,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" s="19">
         <v>46028</v>
@@ -4173,7 +4208,7 @@
         <v>33804</v>
       </c>
       <c r="K61" s="21">
-        <f t="shared" ref="K61:K80" si="10">M61*12</f>
+        <f t="shared" ref="K61:K80" si="11">M61*12</f>
         <v>3621.8571428571427</v>
       </c>
       <c r="L61" s="27">
@@ -4181,13 +4216,14 @@
         <v>30182.142857142859</v>
       </c>
       <c r="M61" s="33">
-        <f t="shared" ref="M61:M80" si="11">I61/112</f>
+        <f t="shared" ref="M61:M80" si="12">I61/112</f>
         <v>301.82142857142856</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>3</v>
+        <f>A61+1</f>
+        <v>2</v>
       </c>
       <c r="C62" s="19">
         <v>46271</v>
@@ -4209,21 +4245,22 @@
         <v>11340</v>
       </c>
       <c r="K62" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1215</v>
       </c>
       <c r="L62" s="27">
-        <f t="shared" ref="L62:L80" si="12">I62-K62</f>
+        <f t="shared" ref="L62:L80" si="13">I62-K62</f>
         <v>10125</v>
       </c>
       <c r="M62" s="33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>101.25</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>4</v>
+        <f t="shared" ref="A63:A81" si="14">A62+1</f>
+        <v>3</v>
       </c>
       <c r="C63" s="19">
         <v>46332</v>
@@ -4245,21 +4282,22 @@
         <v>5670</v>
       </c>
       <c r="K63" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>607.5</v>
       </c>
       <c r="L63" s="27">
+        <f t="shared" si="13"/>
+        <v>5062.5</v>
+      </c>
+      <c r="M63" s="33">
         <f t="shared" si="12"/>
-        <v>5062.5</v>
-      </c>
-      <c r="M63" s="33">
-        <f t="shared" si="11"/>
         <v>50.625</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5</v>
+        <f t="shared" si="14"/>
+        <v>4</v>
       </c>
       <c r="C64" s="19">
         <v>46332</v>
@@ -4281,21 +4319,22 @@
         <v>5616</v>
       </c>
       <c r="K64" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>601.71428571428578</v>
       </c>
       <c r="L64" s="27">
+        <f t="shared" si="13"/>
+        <v>5014.2857142857138</v>
+      </c>
+      <c r="M64" s="33">
         <f t="shared" si="12"/>
-        <v>5014.2857142857138</v>
-      </c>
-      <c r="M64" s="33">
-        <f t="shared" si="11"/>
         <v>50.142857142857146</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>6</v>
+        <f t="shared" si="14"/>
+        <v>5</v>
       </c>
       <c r="C65" s="19" t="s">
         <v>93</v>
@@ -4317,21 +4356,22 @@
         <v>11286</v>
       </c>
       <c r="K65" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1209.2142857142858</v>
       </c>
       <c r="L65" s="27">
+        <f t="shared" si="13"/>
+        <v>10076.785714285714</v>
+      </c>
+      <c r="M65" s="33">
         <f t="shared" si="12"/>
-        <v>10076.785714285714</v>
-      </c>
-      <c r="M65" s="33">
-        <f t="shared" si="11"/>
         <v>100.76785714285714</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>7</v>
+        <f t="shared" si="14"/>
+        <v>6</v>
       </c>
       <c r="C66" s="19" t="s">
         <v>77</v>
@@ -4353,21 +4393,22 @@
         <v>5616</v>
       </c>
       <c r="K66" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>601.71428571428578</v>
       </c>
       <c r="L66" s="27">
+        <f t="shared" si="13"/>
+        <v>5014.2857142857138</v>
+      </c>
+      <c r="M66" s="33">
         <f t="shared" si="12"/>
-        <v>5014.2857142857138</v>
-      </c>
-      <c r="M66" s="33">
-        <f t="shared" si="11"/>
         <v>50.142857142857146</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>8</v>
+        <f t="shared" si="14"/>
+        <v>7</v>
       </c>
       <c r="C67" s="19" t="s">
         <v>98</v>
@@ -4389,21 +4430,22 @@
         <v>5616</v>
       </c>
       <c r="K67" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>601.71428571428578</v>
       </c>
       <c r="L67" s="27">
+        <f t="shared" si="13"/>
+        <v>5014.2857142857138</v>
+      </c>
+      <c r="M67" s="33">
         <f t="shared" si="12"/>
-        <v>5014.2857142857138</v>
-      </c>
-      <c r="M67" s="33">
-        <f t="shared" si="11"/>
         <v>50.142857142857146</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>9</v>
+        <f t="shared" si="14"/>
+        <v>8</v>
       </c>
       <c r="C68" s="19"/>
       <c r="D68" s="20" t="s">
@@ -4419,21 +4461,22 @@
       </c>
       <c r="I68" s="21"/>
       <c r="K68" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L68" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M68" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>9</v>
       </c>
       <c r="C69" s="19"/>
       <c r="D69" s="20" t="s">
@@ -4449,21 +4492,22 @@
       </c>
       <c r="I69" s="21"/>
       <c r="K69" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L69" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>11</v>
+        <f t="shared" si="14"/>
+        <v>10</v>
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="20" t="s">
@@ -4479,21 +4523,22 @@
       </c>
       <c r="I70" s="21"/>
       <c r="K70" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L70" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M70" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M70" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>12</v>
+        <f t="shared" si="14"/>
+        <v>11</v>
       </c>
       <c r="C71" s="19"/>
       <c r="D71" s="20" t="s">
@@ -4509,21 +4554,22 @@
       </c>
       <c r="I71" s="21"/>
       <c r="K71" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L71" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M71" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>13</v>
+        <f t="shared" si="14"/>
+        <v>12</v>
       </c>
       <c r="C72" s="19"/>
       <c r="D72" s="20" t="s">
@@ -4539,21 +4585,22 @@
       </c>
       <c r="I72" s="21"/>
       <c r="K72" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L72" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>14</v>
+        <f t="shared" si="14"/>
+        <v>13</v>
       </c>
       <c r="C73" s="19"/>
       <c r="D73" s="20" t="s">
@@ -4569,21 +4616,22 @@
       </c>
       <c r="I73" s="21"/>
       <c r="K73" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L73" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>15</v>
+        <f t="shared" si="14"/>
+        <v>14</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="20" t="s">
@@ -4599,21 +4647,22 @@
       </c>
       <c r="I74" s="21"/>
       <c r="K74" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L74" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M74" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>16</v>
+        <f t="shared" si="14"/>
+        <v>15</v>
       </c>
       <c r="C75" s="19"/>
       <c r="D75" s="20" t="s">
@@ -4629,21 +4678,22 @@
       </c>
       <c r="I75" s="21"/>
       <c r="K75" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L75" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>17</v>
+        <f t="shared" si="14"/>
+        <v>16</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="20" t="s">
@@ -4659,21 +4709,22 @@
       </c>
       <c r="I76" s="21"/>
       <c r="K76" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L76" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M76" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>18</v>
+        <f t="shared" si="14"/>
+        <v>17</v>
       </c>
       <c r="C77" s="19"/>
       <c r="D77" s="20" t="s">
@@ -4689,21 +4740,22 @@
       </c>
       <c r="I77" s="21"/>
       <c r="K77" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L77" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>19</v>
+        <f t="shared" si="14"/>
+        <v>18</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="s">
@@ -4719,21 +4771,22 @@
       </c>
       <c r="I78" s="21"/>
       <c r="K78" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L78" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M78" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M78" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>20</v>
+        <f t="shared" si="14"/>
+        <v>19</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="20" t="s">
@@ -4749,21 +4802,22 @@
       </c>
       <c r="I79" s="21"/>
       <c r="K79" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L79" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M79" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M79" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>21</v>
+        <f t="shared" si="14"/>
+        <v>20</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="20" t="s">
@@ -4779,21 +4833,22 @@
       </c>
       <c r="I80" s="21"/>
       <c r="K80" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L80" s="27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="33">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>22</v>
+        <f t="shared" si="14"/>
+        <v>21</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="20" t="s">
@@ -4920,7 +4975,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" s="19" t="s">
         <v>76</v>
@@ -4946,21 +5001,22 @@
         <v>16488</v>
       </c>
       <c r="L88" s="21">
-        <f t="shared" ref="L88:L107" si="13">N88*12</f>
+        <f t="shared" ref="L88:L107" si="15">N88*12</f>
         <v>1766.5714285714287</v>
       </c>
       <c r="M88" s="27">
-        <f>K88-L88</f>
+        <f t="shared" ref="M88:M107" si="16">K88-L88</f>
         <v>14721.428571428571</v>
       </c>
       <c r="N88" s="33">
-        <f>K88/112</f>
+        <f t="shared" ref="N88:N107" si="17">K88/112</f>
         <v>147.21428571428572</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>3</v>
+        <f>A88+1</f>
+        <v>2</v>
       </c>
       <c r="C89" s="19" t="s">
         <v>77</v>
@@ -4972,7 +5028,9 @@
       <c r="F89" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G89" s="37"/>
+      <c r="G89" s="37" t="s">
+        <v>105</v>
+      </c>
       <c r="H89" s="20" t="s">
         <v>74</v>
       </c>
@@ -4984,21 +5042,22 @@
         <v>11328</v>
       </c>
       <c r="L89" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1213.7142857142858</v>
       </c>
       <c r="M89" s="27">
-        <f>K89-L89</f>
+        <f t="shared" si="16"/>
         <v>10114.285714285714</v>
       </c>
       <c r="N89" s="33">
-        <f>K89/112</f>
+        <f t="shared" si="17"/>
         <v>101.14285714285714</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>4</v>
+        <f t="shared" ref="A90:A108" si="18">A89+1</f>
+        <v>3</v>
       </c>
       <c r="C90" s="19" t="s">
         <v>78</v>
@@ -5010,7 +5069,9 @@
       <c r="F90" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G90" s="37"/>
+      <c r="G90" s="37" t="s">
+        <v>106</v>
+      </c>
       <c r="H90" s="20" t="s">
         <v>74</v>
       </c>
@@ -5022,21 +5083,22 @@
         <v>11016</v>
       </c>
       <c r="L90" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1180.2857142857142</v>
       </c>
       <c r="M90" s="27">
-        <f>K90-L90</f>
+        <f t="shared" si="16"/>
         <v>9835.7142857142862</v>
       </c>
       <c r="N90" s="33">
-        <f>K90/112</f>
+        <f t="shared" si="17"/>
         <v>98.357142857142861</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>5</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="C91" s="19" t="s">
         <v>79</v>
@@ -5048,7 +5110,9 @@
       <c r="F91" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G91" s="37"/>
+      <c r="G91" s="37" t="s">
+        <v>107</v>
+      </c>
       <c r="H91" s="20" t="s">
         <v>74</v>
       </c>
@@ -5060,21 +5124,22 @@
         <v>13800</v>
       </c>
       <c r="L91" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1478.5714285714284</v>
       </c>
       <c r="M91" s="27">
-        <f>K91-L91</f>
+        <f t="shared" si="16"/>
         <v>12321.428571428572</v>
       </c>
       <c r="N91" s="33">
-        <f>K91/112</f>
+        <f t="shared" si="17"/>
         <v>123.21428571428571</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>6</v>
+        <f t="shared" si="18"/>
+        <v>5</v>
       </c>
       <c r="C92" s="19" t="s">
         <v>80</v>
@@ -5086,7 +5151,9 @@
       <c r="F92" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="37"/>
+      <c r="G92" s="37" t="s">
+        <v>108</v>
+      </c>
       <c r="H92" s="20" t="s">
         <v>74</v>
       </c>
@@ -5098,21 +5165,22 @@
         <v>11016</v>
       </c>
       <c r="L92" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1180.2857142857142</v>
       </c>
       <c r="M92" s="27">
-        <f>K92-L92</f>
+        <f t="shared" si="16"/>
         <v>9835.7142857142862</v>
       </c>
       <c r="N92" s="33">
-        <f>K92/112</f>
+        <f t="shared" si="17"/>
         <v>98.357142857142861</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>7</v>
+        <f t="shared" si="18"/>
+        <v>6</v>
       </c>
       <c r="C93" s="19" t="s">
         <v>80</v>
@@ -5124,7 +5192,9 @@
       <c r="F93" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G93" s="37"/>
+      <c r="G93" s="37" t="s">
+        <v>109</v>
+      </c>
       <c r="H93" s="20" t="s">
         <v>74</v>
       </c>
@@ -5136,21 +5206,22 @@
         <v>11016</v>
       </c>
       <c r="L93" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1180.2857142857142</v>
       </c>
       <c r="M93" s="27">
-        <f>K93-L93</f>
+        <f t="shared" si="16"/>
         <v>9835.7142857142862</v>
       </c>
       <c r="N93" s="33">
-        <f>K93/112</f>
+        <f t="shared" si="17"/>
         <v>98.357142857142861</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>8</v>
+        <f t="shared" si="18"/>
+        <v>7</v>
       </c>
       <c r="C94" s="19"/>
       <c r="D94" s="20" t="s">
@@ -5168,21 +5239,22 @@
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
       <c r="L94" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M94" s="27">
-        <f>K94-L94</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N94" s="33">
-        <f>K94/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>9</v>
+        <f t="shared" si="18"/>
+        <v>8</v>
       </c>
       <c r="C95" s="19"/>
       <c r="D95" s="20" t="s">
@@ -5200,21 +5272,22 @@
       <c r="J95" s="21"/>
       <c r="K95" s="21"/>
       <c r="L95" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M95" s="27">
-        <f>K95-L95</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N95" s="33">
-        <f>K95/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>10</v>
+        <f t="shared" si="18"/>
+        <v>9</v>
       </c>
       <c r="C96" s="19"/>
       <c r="D96" s="20" t="s">
@@ -5232,21 +5305,22 @@
       <c r="J96" s="21"/>
       <c r="K96" s="21"/>
       <c r="L96" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M96" s="27">
-        <f>K96-L96</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N96" s="33">
-        <f>K96/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>11</v>
+        <f t="shared" si="18"/>
+        <v>10</v>
       </c>
       <c r="C97" s="19"/>
       <c r="D97" s="20" t="s">
@@ -5264,21 +5338,22 @@
       <c r="J97" s="21"/>
       <c r="K97" s="21"/>
       <c r="L97" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M97" s="27">
-        <f>K97-L97</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N97" s="33">
-        <f>K97/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>12</v>
+        <f t="shared" si="18"/>
+        <v>11</v>
       </c>
       <c r="C98" s="19"/>
       <c r="D98" s="20" t="s">
@@ -5296,21 +5371,22 @@
       <c r="J98" s="21"/>
       <c r="K98" s="21"/>
       <c r="L98" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M98" s="27">
-        <f>K98-L98</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N98" s="33">
-        <f>K98/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>13</v>
+        <f t="shared" si="18"/>
+        <v>12</v>
       </c>
       <c r="C99" s="19"/>
       <c r="D99" s="20" t="s">
@@ -5328,21 +5404,22 @@
       <c r="J99" s="21"/>
       <c r="K99" s="21"/>
       <c r="L99" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M99" s="27">
-        <f>K99-L99</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N99" s="33">
-        <f>K99/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>14</v>
+        <f t="shared" si="18"/>
+        <v>13</v>
       </c>
       <c r="C100" s="19"/>
       <c r="D100" s="20" t="s">
@@ -5360,21 +5437,22 @@
       <c r="J100" s="21"/>
       <c r="K100" s="21"/>
       <c r="L100" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M100" s="27">
-        <f>K100-L100</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N100" s="33">
-        <f>K100/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>15</v>
+        <f t="shared" si="18"/>
+        <v>14</v>
       </c>
       <c r="C101" s="19"/>
       <c r="D101" s="20" t="s">
@@ -5392,21 +5470,22 @@
       <c r="J101" s="21"/>
       <c r="K101" s="21"/>
       <c r="L101" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M101" s="27">
-        <f>K101-L101</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N101" s="33">
-        <f>K101/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>16</v>
+        <f t="shared" si="18"/>
+        <v>15</v>
       </c>
       <c r="C102" s="19"/>
       <c r="D102" s="20" t="s">
@@ -5424,21 +5503,22 @@
       <c r="J102" s="21"/>
       <c r="K102" s="21"/>
       <c r="L102" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M102" s="27">
-        <f>K102-L102</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N102" s="33">
-        <f>K102/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>17</v>
+        <f t="shared" si="18"/>
+        <v>16</v>
       </c>
       <c r="C103" s="19"/>
       <c r="D103" s="20" t="s">
@@ -5456,21 +5536,22 @@
       <c r="J103" s="21"/>
       <c r="K103" s="21"/>
       <c r="L103" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M103" s="27">
-        <f>K103-L103</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N103" s="33">
-        <f>K103/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>18</v>
+        <f t="shared" si="18"/>
+        <v>17</v>
       </c>
       <c r="C104" s="19"/>
       <c r="D104" s="20" t="s">
@@ -5488,21 +5569,22 @@
       <c r="J104" s="21"/>
       <c r="K104" s="21"/>
       <c r="L104" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M104" s="27">
-        <f>K104-L104</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N104" s="33">
-        <f>K104/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>19</v>
+        <f t="shared" si="18"/>
+        <v>18</v>
       </c>
       <c r="C105" s="19"/>
       <c r="D105" s="20" t="s">
@@ -5520,21 +5602,22 @@
       <c r="J105" s="21"/>
       <c r="K105" s="21"/>
       <c r="L105" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M105" s="27">
-        <f>K105-L105</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N105" s="33">
-        <f>K105/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>20</v>
+        <f t="shared" si="18"/>
+        <v>19</v>
       </c>
       <c r="C106" s="19"/>
       <c r="D106" s="20" t="s">
@@ -5552,21 +5635,22 @@
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
       <c r="L106" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M106" s="27">
-        <f>K106-L106</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N106" s="33">
-        <f>K106/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>21</v>
+        <f t="shared" si="18"/>
+        <v>20</v>
       </c>
       <c r="C107" s="19"/>
       <c r="D107" s="20" t="s">
@@ -5584,21 +5668,22 @@
       <c r="J107" s="21"/>
       <c r="K107" s="21"/>
       <c r="L107" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M107" s="27">
-        <f>K107-L107</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N107" s="33">
-        <f>K107/112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>22</v>
+        <f t="shared" si="18"/>
+        <v>21</v>
       </c>
       <c r="C108" s="19"/>
       <c r="D108" s="20" t="s">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47768989-1745-42BC-A69F-D410D09D3130}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1DA5E4-B244-44CF-9297-1EFEE86D3BE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="111">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>06</t>
+  </si>
+  <si>
+    <t>06/25/2026</t>
   </si>
 </sst>
 </file>
@@ -2723,7 +2726,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>110</v>
+      </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
       </c>
@@ -2731,22 +2736,27 @@
       <c r="F13" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20">
+        <v>518764026</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K13" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L13" s="27">
         <f>I13-K13</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M13" s="33">
         <f>I13/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -3243,7 +3253,7 @@
       <c r="G28"/>
       <c r="I28" s="44">
         <f>SUM(I7:I27)</f>
-        <v>7691778.1600000001</v>
+        <v>9028129.120000001</v>
       </c>
       <c r="J28" s="44">
         <f ca="1">SUM(J7:J31)</f>
@@ -3251,15 +3261,15 @@
       </c>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>824119.08857142855</v>
+        <v>967299.54857142852</v>
       </c>
       <c r="L28" s="44">
         <f>SUM(L7:L27)</f>
-        <v>6867659.0714285718</v>
+        <v>8060829.5714285718</v>
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>68676.590714285718</v>
+        <v>80608.295714285719</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1DA5E4-B244-44CF-9297-1EFEE86D3BE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F561BFFE-9E53-4965-8FCE-F520F90F7F55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="112">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>06/25/2026</t>
+  </si>
+  <si>
+    <t>R16</t>
   </si>
 </sst>
 </file>
@@ -4457,7 +4460,9 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="C68" s="19"/>
+      <c r="C68" s="19" t="s">
+        <v>110</v>
+      </c>
       <c r="D68" s="20" t="s">
         <v>68</v>
       </c>
@@ -4465,22 +4470,26 @@
       <c r="F68" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G68" s="37"/>
+      <c r="G68" s="37" t="s">
+        <v>111</v>
+      </c>
       <c r="H68" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I68" s="21"/>
+      <c r="I68" s="21">
+        <v>5670</v>
+      </c>
       <c r="K68" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>607.5</v>
       </c>
       <c r="L68" s="27">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5062.5</v>
       </c>
       <c r="M68" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50.625</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -4880,7 +4889,7 @@
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I82" s="44">
         <f>SUM(I61:I81)</f>
-        <v>78948</v>
+        <v>84618</v>
       </c>
       <c r="J82" s="44">
         <f ca="1">SUM(J61:J85)</f>
@@ -4888,15 +4897,15 @@
       </c>
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>8458.7142857142881</v>
+        <v>9066.2142857142881</v>
       </c>
       <c r="L82" s="44">
         <f>SUM(L61:L81)</f>
-        <v>70489.285714285696</v>
+        <v>75551.785714285696</v>
       </c>
       <c r="M82" s="45">
         <f>SUM(M61:M81)</f>
-        <v>704.89285714285711</v>
+        <v>755.51785714285711</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F561BFFE-9E53-4965-8FCE-F520F90F7F55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AAD831-649B-4F54-8D2D-30819AEA647B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="114">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>R16</t>
+  </si>
+  <si>
+    <t>06/26/2026</t>
+  </si>
+  <si>
+    <t>R17</t>
   </si>
 </sst>
 </file>
@@ -2771,7 +2777,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>112</v>
+      </c>
       <c r="D14" s="20" t="s">
         <v>68</v>
       </c>
@@ -2779,22 +2787,27 @@
       <c r="F14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20">
+        <v>518768055</v>
+      </c>
       <c r="H14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="36"/>
+      <c r="I14" s="36">
+        <f>1397196-81234.18</f>
+        <v>1315961.82</v>
+      </c>
       <c r="K14" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>140995.9092857143</v>
       </c>
       <c r="L14" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1174965.9107142857</v>
       </c>
       <c r="M14" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11749.659107142857</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2806,7 +2819,9 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>112</v>
+      </c>
       <c r="D15" s="20" t="s">
         <v>68</v>
       </c>
@@ -2814,22 +2829,27 @@
       <c r="F15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="20">
+        <v>518768254</v>
+      </c>
       <c r="H15" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K15" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L15" s="27">
         <f>I15-K15</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M15" s="33">
         <f>I15/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -3256,7 +3276,7 @@
       <c r="G28"/>
       <c r="I28" s="44">
         <f>SUM(I7:I27)</f>
-        <v>9028129.120000001</v>
+        <v>11680441.900000002</v>
       </c>
       <c r="J28" s="44">
         <f ca="1">SUM(J7:J31)</f>
@@ -3264,15 +3284,15 @@
       </c>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>967299.54857142852</v>
+        <v>1251475.9178571429</v>
       </c>
       <c r="L28" s="44">
         <f>SUM(L7:L27)</f>
-        <v>8060829.5714285718</v>
+        <v>10428965.982142858</v>
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>80608.295714285719</v>
+        <v>104289.65982142858</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -3919,7 +3939,9 @@
         <f t="shared" si="10"/>
         <v>16</v>
       </c>
-      <c r="C49" s="19"/>
+      <c r="C49" s="19" t="s">
+        <v>112</v>
+      </c>
       <c r="D49" s="20" t="s">
         <v>68</v>
       </c>
@@ -3927,22 +3949,27 @@
       <c r="F49" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G49" s="37"/>
+      <c r="G49" s="37" t="s">
+        <v>113</v>
+      </c>
       <c r="H49" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I49" s="21"/>
+      <c r="I49" s="21">
+        <f>11988+10656+95904</f>
+        <v>118548</v>
+      </c>
       <c r="K49" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12701.571428571429</v>
       </c>
       <c r="L49" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>105846.42857142857</v>
       </c>
       <c r="M49" s="33">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1058.4642857142858</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -4094,7 +4121,7 @@
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I55" s="44">
         <f>SUM(I34:I54)</f>
-        <v>2608824</v>
+        <v>2727372</v>
       </c>
       <c r="J55" s="44">
         <f ca="1">SUM(J34:J58)</f>
@@ -4102,15 +4129,15 @@
       </c>
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>279516.85714285716</v>
+        <v>292218.42857142858</v>
       </c>
       <c r="L55" s="44">
         <f>SUM(L34:L54)</f>
-        <v>2329307.1428571427</v>
+        <v>2435153.5714285714</v>
       </c>
       <c r="M55" s="45">
         <f>SUM(M34:M54)</f>
-        <v>23293.071428571428</v>
+        <v>24351.535714285714</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -4497,7 +4524,9 @@
         <f t="shared" si="14"/>
         <v>9</v>
       </c>
-      <c r="C69" s="19"/>
+      <c r="C69" s="19" t="s">
+        <v>112</v>
+      </c>
       <c r="D69" s="20" t="s">
         <v>68</v>
       </c>
@@ -4505,22 +4534,26 @@
       <c r="F69" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G69" s="37"/>
+      <c r="G69" s="37" t="s">
+        <v>113</v>
+      </c>
       <c r="H69" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I69" s="21"/>
+      <c r="I69" s="21">
+        <v>5616</v>
+      </c>
       <c r="K69" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>601.71428571428578</v>
       </c>
       <c r="L69" s="27">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5014.2857142857138</v>
       </c>
       <c r="M69" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50.142857142857146</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -4889,7 +4922,7 @@
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I82" s="44">
         <f>SUM(I61:I81)</f>
-        <v>84618</v>
+        <v>90234</v>
       </c>
       <c r="J82" s="44">
         <f ca="1">SUM(J61:J85)</f>
@@ -4897,15 +4930,15 @@
       </c>
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>9066.2142857142881</v>
+        <v>9667.9285714285743</v>
       </c>
       <c r="L82" s="44">
         <f>SUM(L61:L81)</f>
-        <v>75551.785714285696</v>
+        <v>80566.071428571406</v>
       </c>
       <c r="M82" s="45">
         <f>SUM(M61:M81)</f>
-        <v>755.51785714285711</v>
+        <v>805.66071428571422</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AAD831-649B-4F54-8D2D-30819AEA647B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4D4606-D089-4F15-97B2-FB5E8DB0EE33}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2355,7 +2355,7 @@
     <col min="2" max="2" width="4.5703125" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="30.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="68.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="38" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4D4606-D089-4F15-97B2-FB5E8DB0EE33}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BB822-D589-4B0B-9CAD-E2A6DF7E407A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="119">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -375,6 +375,21 @@
   </si>
   <si>
     <t>R17</t>
+  </si>
+  <si>
+    <t>AMOUNT</t>
+  </si>
+  <si>
+    <t>OF PRODUCTS</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>DISCOUNT</t>
+  </si>
+  <si>
+    <t>06/27/2026</t>
   </si>
 </sst>
 </file>
@@ -2348,7 +2363,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{423D5057-7111-4BE4-94EA-57775A7107A8}">
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
@@ -2359,15 +2374,15 @@
     <col min="6" max="6" width="68.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="38" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" customWidth="1"/>
-    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="14" style="35" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="14" style="35" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C1" s="39" t="s">
         <v>67</v>
       </c>
@@ -2377,11 +2392,13 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="28"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="28"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -2389,11 +2406,13 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="29"/>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="29"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="41" t="s">
         <v>81</v>
       </c>
@@ -2405,11 +2424,13 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="28"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="28"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -2417,11 +2438,13 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="30"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="30"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2430,16 +2453,22 @@
         <v>2</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10" t="s">
+      <c r="M5" s="10"/>
+      <c r="N5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="31"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O5" s="31"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -2461,20 +2490,26 @@
       <c r="H6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="M6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="N6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="32">
+      <c r="O6" s="32">
         <v>2307</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2498,25 +2533,33 @@
         <v>74</v>
       </c>
       <c r="I7" s="21">
+        <f>1315032</f>
+        <v>1315032</v>
+      </c>
+      <c r="J7" s="21">
+        <f>273031.68</f>
+        <v>273031.67999999999</v>
+      </c>
+      <c r="K7" s="21">
         <f>1315032-273031.68</f>
         <v>1042000.3200000001</v>
       </c>
-      <c r="K7" s="21">
-        <f>M7*12</f>
+      <c r="M7" s="21">
+        <f>O7*12</f>
         <v>111642.89142857144</v>
       </c>
-      <c r="L7" s="27">
-        <f>I7-K7</f>
+      <c r="N7" s="27">
+        <f>K7-M7</f>
         <v>930357.42857142864</v>
       </c>
-      <c r="M7" s="33">
-        <f>I7/112</f>
+      <c r="O7" s="33">
+        <f>K7/112</f>
         <v>9303.5742857142868</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>A7+1</f>
         <v>2</v>
@@ -2542,23 +2585,31 @@
         <v>74</v>
       </c>
       <c r="I8" s="21">
+        <f>1412471</f>
+        <v>1412471</v>
+      </c>
+      <c r="J8" s="21">
+        <f>61256.62</f>
+        <v>61256.62</v>
+      </c>
+      <c r="K8" s="21">
         <f>1412471-61256.62</f>
         <v>1351214.38</v>
       </c>
-      <c r="K8" s="21">
-        <f>M8*12</f>
+      <c r="M8" s="21">
+        <f>O8*12</f>
         <v>144772.96928571427</v>
       </c>
-      <c r="L8" s="27">
-        <f>I8-K8</f>
+      <c r="N8" s="27">
+        <f>K8-M8</f>
         <v>1206441.4107142857</v>
       </c>
-      <c r="M8" s="33">
-        <f t="shared" ref="M8:M26" si="0">I8/112</f>
+      <c r="O8" s="33">
+        <f t="shared" ref="O8:O26" si="0">K8/112</f>
         <v>12064.414107142857</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" ref="A9:B27" si="1">A8+1</f>
         <v>3</v>
@@ -2584,23 +2635,31 @@
         <v>74</v>
       </c>
       <c r="I9" s="21">
+        <f>1397196</f>
+        <v>1397196</v>
+      </c>
+      <c r="J9" s="21">
+        <f>60845.04</f>
+        <v>60845.04</v>
+      </c>
+      <c r="K9" s="21">
         <f>1397196-60845.04</f>
         <v>1336350.96</v>
       </c>
-      <c r="K9" s="21">
-        <f t="shared" ref="K9:K26" si="2">M9*12</f>
+      <c r="M9" s="21">
+        <f t="shared" ref="M9:M26" si="2">O9*12</f>
         <v>143180.46</v>
       </c>
-      <c r="L9" s="27">
-        <f t="shared" ref="L9:L26" si="3">I9-K9</f>
+      <c r="N9" s="27">
+        <f t="shared" ref="N9:N26" si="3">K9-M9</f>
         <v>1193170.5</v>
       </c>
-      <c r="M9" s="33">
+      <c r="O9" s="33">
         <f t="shared" si="0"/>
         <v>11931.705</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -2626,23 +2685,31 @@
         <v>74</v>
       </c>
       <c r="I10" s="21">
+        <f>1346606</f>
+        <v>1346606</v>
+      </c>
+      <c r="J10" s="21">
+        <f>57095.42</f>
+        <v>57095.42</v>
+      </c>
+      <c r="K10" s="21">
         <f>1346606-57095.42</f>
         <v>1289510.58</v>
       </c>
-      <c r="K10" s="21">
+      <c r="M10" s="21">
         <f t="shared" si="2"/>
         <v>138161.84785714286</v>
       </c>
-      <c r="L10" s="27">
+      <c r="N10" s="27">
         <f t="shared" si="3"/>
         <v>1151348.7321428573</v>
       </c>
-      <c r="M10" s="33">
+      <c r="O10" s="33">
         <f t="shared" si="0"/>
         <v>11513.487321428573</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -2668,23 +2735,31 @@
         <v>74</v>
       </c>
       <c r="I11" s="21">
+        <f>1397196</f>
+        <v>1397196</v>
+      </c>
+      <c r="J11" s="21">
+        <f>60845.04</f>
+        <v>60845.04</v>
+      </c>
+      <c r="K11" s="21">
         <f>1397196-60845.04</f>
         <v>1336350.96</v>
       </c>
-      <c r="K11" s="21">
+      <c r="M11" s="21">
         <f t="shared" si="2"/>
         <v>143180.46</v>
       </c>
-      <c r="L11" s="27">
+      <c r="N11" s="27">
         <f t="shared" si="3"/>
         <v>1193170.5</v>
       </c>
-      <c r="M11" s="33">
+      <c r="O11" s="33">
         <f t="shared" si="0"/>
         <v>11931.705</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2710,23 +2785,31 @@
         <v>74</v>
       </c>
       <c r="I12" s="21">
+        <f>1397196</f>
+        <v>1397196</v>
+      </c>
+      <c r="J12" s="21">
+        <f>60845.04</f>
+        <v>60845.04</v>
+      </c>
+      <c r="K12" s="21">
         <f>1397196-60845.04</f>
         <v>1336350.96</v>
       </c>
-      <c r="K12" s="21">
+      <c r="M12" s="21">
         <f t="shared" si="2"/>
         <v>143180.46</v>
       </c>
-      <c r="L12" s="27">
+      <c r="N12" s="27">
         <f t="shared" si="3"/>
         <v>1193170.5</v>
       </c>
-      <c r="M12" s="33">
+      <c r="O12" s="33">
         <f t="shared" si="0"/>
         <v>11931.705</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -2752,23 +2835,31 @@
         <v>74</v>
       </c>
       <c r="I13" s="21">
+        <f>1397196</f>
+        <v>1397196</v>
+      </c>
+      <c r="J13" s="21">
+        <f>60845.04</f>
+        <v>60845.04</v>
+      </c>
+      <c r="K13" s="21">
         <f>1397196-60845.04</f>
         <v>1336350.96</v>
       </c>
-      <c r="K13" s="21">
+      <c r="M13" s="21">
         <f t="shared" si="2"/>
         <v>143180.46</v>
       </c>
-      <c r="L13" s="27">
-        <f>I13-K13</f>
+      <c r="N13" s="27">
+        <f>K13-M13</f>
         <v>1193170.5</v>
       </c>
-      <c r="M13" s="33">
-        <f>I13/112</f>
+      <c r="O13" s="33">
+        <f>K13/112</f>
         <v>11931.705</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -2794,23 +2885,31 @@
         <v>74</v>
       </c>
       <c r="I14" s="36">
+        <f>1397196</f>
+        <v>1397196</v>
+      </c>
+      <c r="J14" s="36">
+        <f>81234.18</f>
+        <v>81234.179999999993</v>
+      </c>
+      <c r="K14" s="36">
         <f>1397196-81234.18</f>
         <v>1315961.82</v>
       </c>
-      <c r="K14" s="21">
+      <c r="M14" s="21">
         <f t="shared" si="2"/>
         <v>140995.9092857143</v>
       </c>
-      <c r="L14" s="27">
+      <c r="N14" s="27">
         <f t="shared" si="3"/>
         <v>1174965.9107142857</v>
       </c>
-      <c r="M14" s="33">
+      <c r="O14" s="33">
         <f t="shared" si="0"/>
         <v>11749.659107142857</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -2836,23 +2935,31 @@
         <v>74</v>
       </c>
       <c r="I15" s="21">
+        <f>1397196</f>
+        <v>1397196</v>
+      </c>
+      <c r="J15" s="21">
+        <f>60845.04</f>
+        <v>60845.04</v>
+      </c>
+      <c r="K15" s="21">
         <f>1397196-60845.04</f>
         <v>1336350.96</v>
       </c>
-      <c r="K15" s="21">
+      <c r="M15" s="21">
         <f t="shared" si="2"/>
         <v>143180.46</v>
       </c>
-      <c r="L15" s="27">
-        <f>I15-K15</f>
+      <c r="N15" s="27">
+        <f>K15-M15</f>
         <v>1193170.5</v>
       </c>
-      <c r="M15" s="33">
-        <f>I15/112</f>
+      <c r="O15" s="33">
+        <f>K15/112</f>
         <v>11931.705</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2861,7 +2968,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>118</v>
+      </c>
       <c r="D16" s="20" t="s">
         <v>68</v>
       </c>
@@ -2869,25 +2978,36 @@
       <c r="F16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20">
+        <v>518772648</v>
+      </c>
       <c r="H16" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="21">
+        <v>1155198</v>
+      </c>
+      <c r="J16" s="21">
+        <v>50306.52</v>
+      </c>
       <c r="K16" s="21">
+        <f>I16-J16</f>
+        <v>1104891.48</v>
+      </c>
+      <c r="M16" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="27">
+        <v>118381.22999999998</v>
+      </c>
+      <c r="N16" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="33">
+        <v>986510.25</v>
+      </c>
+      <c r="O16" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>9865.1024999999991</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -2896,7 +3016,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>118</v>
+      </c>
       <c r="D17" s="20" t="s">
         <v>68</v>
       </c>
@@ -2904,25 +3026,36 @@
       <c r="F17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="20">
+        <v>518772163</v>
+      </c>
       <c r="H17" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J17" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K17" s="21">
+        <f t="shared" ref="K17:K27" si="4">I17-J17</f>
+        <v>1336350.96</v>
+      </c>
+      <c r="M17" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="27">
+        <v>143180.46</v>
+      </c>
+      <c r="N17" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="33">
+        <v>1193170.5</v>
+      </c>
+      <c r="O17" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>11931.705</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -2944,20 +3077,25 @@
         <v>74</v>
       </c>
       <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
       <c r="K18" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="27">
+      <c r="N18" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="33">
+      <c r="O18" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -2979,20 +3117,25 @@
         <v>74</v>
       </c>
       <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
       <c r="K19" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="27">
+      <c r="N19" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="33">
+      <c r="O19" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -3014,20 +3157,25 @@
         <v>74</v>
       </c>
       <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
       <c r="K20" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="27">
+      <c r="N20" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="33">
+      <c r="O20" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -3049,20 +3197,25 @@
         <v>74</v>
       </c>
       <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
       <c r="K21" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="27">
+      <c r="N21" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="33">
+      <c r="O21" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -3084,20 +3237,25 @@
         <v>74</v>
       </c>
       <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
       <c r="K22" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="27">
+      <c r="N22" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M22" s="33">
+      <c r="O22" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -3119,20 +3277,25 @@
         <v>74</v>
       </c>
       <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
       <c r="K23" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="27">
+      <c r="N23" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M23" s="33">
+      <c r="O23" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -3154,20 +3317,25 @@
         <v>74</v>
       </c>
       <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
       <c r="K24" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="27">
+      <c r="N24" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M24" s="33">
+      <c r="O24" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -3189,20 +3357,25 @@
         <v>74</v>
       </c>
       <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
       <c r="K25" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="27">
+      <c r="N25" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M25" s="33">
+      <c r="O25" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -3224,20 +3397,25 @@
         <v>74</v>
       </c>
       <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
       <c r="K26" s="21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="27">
+      <c r="N26" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M26" s="33">
+      <c r="O26" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -3259,47 +3437,60 @@
         <v>74</v>
       </c>
       <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
       <c r="K27" s="21">
-        <f t="shared" ref="K27" si="4">M27*12</f>
-        <v>0</v>
-      </c>
-      <c r="L27" s="27">
-        <f t="shared" ref="L27" si="5">I27-K27</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="33">
-        <f t="shared" ref="M27" si="6">I27/112</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="21">
+        <f t="shared" ref="M27" si="5">O27*12</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="27">
+        <f t="shared" ref="N27" si="6">K27-M27</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="33">
+        <f t="shared" ref="O27" si="7">K27/112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G28"/>
       <c r="I28" s="44">
-        <f>SUM(I7:I27)</f>
-        <v>11680441.900000002</v>
+        <f t="shared" ref="I28:J28" si="8">SUM(I7:I27)</f>
+        <v>15009679</v>
       </c>
       <c r="J28" s="44">
-        <f ca="1">SUM(J7:J31)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>887994.66000000015</v>
       </c>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>1251475.9178571429</v>
+        <v>14121684.340000004</v>
       </c>
       <c r="L28" s="44">
-        <f>SUM(L7:L27)</f>
-        <v>10428965.982142858</v>
+        <f ca="1">SUM(L7:L31)</f>
+        <v>0</v>
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>104289.65982142858</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1513037.6078571428</v>
+      </c>
+      <c r="N28" s="44">
+        <f>SUM(N7:N27)</f>
+        <v>12608646.732142858</v>
+      </c>
+      <c r="O28" s="44">
+        <f>SUM(O7:O27)</f>
+        <v>126086.46732142857</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G29"/>
-      <c r="M29" s="34"/>
-    </row>
-    <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="O29" s="34"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C30" s="41" t="s">
         <v>82</v>
       </c>
@@ -3311,11 +3502,13 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="28"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="28"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -3323,11 +3516,13 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
       <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="30"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="30"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -3336,16 +3531,22 @@
         <v>2</v>
       </c>
       <c r="H32" s="9"/>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K32" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10" t="s">
+      <c r="M32" s="10"/>
+      <c r="N32" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="31"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O32" s="31"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -3367,20 +3568,26 @@
       <c r="H33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K33" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="M33" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="N33" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M33" s="32">
+      <c r="O33" s="32">
         <v>2307</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
@@ -3400,23 +3607,25 @@
       <c r="H34" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="21">
         <v>105480</v>
       </c>
-      <c r="K34" s="21">
-        <f t="shared" ref="K34:K53" si="7">M34*12</f>
+      <c r="M34" s="21">
+        <f t="shared" ref="M34:M53" si="9">O34*12</f>
         <v>11301.428571428572</v>
       </c>
-      <c r="L34" s="27">
-        <f>I34-K34</f>
+      <c r="N34" s="27">
+        <f>K34-M34</f>
         <v>94178.57142857142</v>
       </c>
-      <c r="M34" s="33">
-        <f t="shared" ref="M34:M53" si="8">I34/112</f>
+      <c r="O34" s="33">
+        <f t="shared" ref="O34:O53" si="10">K34/112</f>
         <v>941.78571428571433</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
         <f>A34+1</f>
         <v>2</v>
@@ -3437,25 +3646,27 @@
       <c r="H35" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="21">
         <v>199368</v>
       </c>
-      <c r="K35" s="21">
-        <f t="shared" si="7"/>
+      <c r="M35" s="21">
+        <f t="shared" si="9"/>
         <v>21360.857142857145</v>
       </c>
-      <c r="L35" s="27">
-        <f t="shared" ref="L35:L53" si="9">I35-K35</f>
+      <c r="N35" s="27">
+        <f t="shared" ref="N35:N53" si="11">K35-M35</f>
         <v>178007.14285714284</v>
       </c>
-      <c r="M35" s="33">
-        <f t="shared" si="8"/>
+      <c r="O35" s="33">
+        <f t="shared" si="10"/>
         <v>1780.0714285714287</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
-        <f t="shared" ref="A36:A54" si="10">A35+1</f>
+        <f t="shared" ref="A36:A54" si="12">A35+1</f>
         <v>3</v>
       </c>
       <c r="C36" s="19">
@@ -3474,25 +3685,27 @@
       <c r="H36" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="21">
         <v>177156</v>
       </c>
-      <c r="K36" s="21">
-        <f t="shared" si="7"/>
+      <c r="M36" s="21">
+        <f t="shared" si="9"/>
         <v>18981</v>
       </c>
-      <c r="L36" s="27">
-        <f t="shared" si="9"/>
+      <c r="N36" s="27">
+        <f t="shared" si="11"/>
         <v>158175</v>
       </c>
-      <c r="M36" s="33">
-        <f t="shared" si="8"/>
+      <c r="O36" s="33">
+        <f t="shared" si="10"/>
         <v>1581.75</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C37" s="19">
@@ -3511,25 +3724,27 @@
       <c r="H37" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="21">
         <v>203796</v>
       </c>
-      <c r="K37" s="21">
-        <f t="shared" si="7"/>
+      <c r="M37" s="21">
+        <f t="shared" si="9"/>
         <v>21835.285714285714</v>
       </c>
-      <c r="L37" s="27">
-        <f t="shared" si="9"/>
+      <c r="N37" s="27">
+        <f t="shared" si="11"/>
         <v>181960.71428571429</v>
       </c>
-      <c r="M37" s="33">
-        <f t="shared" si="8"/>
+      <c r="O37" s="33">
+        <f t="shared" si="10"/>
         <v>1819.6071428571429</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="C38" s="19">
@@ -3548,25 +3763,27 @@
       <c r="H38" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="21">
         <v>187884</v>
       </c>
-      <c r="K38" s="21">
-        <f t="shared" si="7"/>
+      <c r="M38" s="21">
+        <f t="shared" si="9"/>
         <v>20130.428571428572</v>
       </c>
-      <c r="L38" s="27">
-        <f t="shared" si="9"/>
+      <c r="N38" s="27">
+        <f t="shared" si="11"/>
         <v>167753.57142857142</v>
       </c>
-      <c r="M38" s="33">
-        <f t="shared" si="8"/>
+      <c r="O38" s="33">
+        <f t="shared" si="10"/>
         <v>1677.5357142857142</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="C39" s="19">
@@ -3585,25 +3802,27 @@
       <c r="H39" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="21">
         <v>191808</v>
       </c>
-      <c r="K39" s="21">
-        <f t="shared" si="7"/>
+      <c r="M39" s="21">
+        <f t="shared" si="9"/>
         <v>20550.857142857145</v>
       </c>
-      <c r="L39" s="27">
-        <f t="shared" si="9"/>
+      <c r="N39" s="27">
+        <f t="shared" si="11"/>
         <v>171257.14285714284</v>
       </c>
-      <c r="M39" s="33">
-        <f t="shared" si="8"/>
+      <c r="O39" s="33">
+        <f t="shared" si="10"/>
         <v>1712.5714285714287</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="C40" s="19">
@@ -3622,25 +3841,27 @@
       <c r="H40" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="21">
         <v>203796</v>
       </c>
-      <c r="K40" s="21">
-        <f t="shared" si="7"/>
+      <c r="M40" s="21">
+        <f t="shared" si="9"/>
         <v>21835.285714285714</v>
       </c>
-      <c r="L40" s="27">
-        <f t="shared" si="9"/>
+      <c r="N40" s="27">
+        <f t="shared" si="11"/>
         <v>181960.71428571429</v>
       </c>
-      <c r="M40" s="33">
-        <f t="shared" si="8"/>
+      <c r="O40" s="33">
+        <f t="shared" si="10"/>
         <v>1819.6071428571429</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="C41" s="19" t="s">
@@ -3659,25 +3880,27 @@
       <c r="H41" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="21">
         <v>190800</v>
       </c>
-      <c r="K41" s="21">
-        <f t="shared" si="7"/>
+      <c r="M41" s="21">
+        <f t="shared" si="9"/>
         <v>20442.857142857145</v>
       </c>
-      <c r="L41" s="27">
-        <f t="shared" si="9"/>
+      <c r="N41" s="27">
+        <f t="shared" si="11"/>
         <v>170357.14285714284</v>
       </c>
-      <c r="M41" s="33">
-        <f t="shared" si="8"/>
+      <c r="O41" s="33">
+        <f t="shared" si="10"/>
         <v>1703.5714285714287</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="C42" s="19" t="s">
@@ -3696,25 +3919,27 @@
       <c r="H42" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="21">
         <v>149328</v>
       </c>
-      <c r="K42" s="21">
-        <f t="shared" si="7"/>
+      <c r="M42" s="21">
+        <f t="shared" si="9"/>
         <v>15999.428571428571</v>
       </c>
-      <c r="L42" s="27">
-        <f t="shared" si="9"/>
+      <c r="N42" s="27">
+        <f t="shared" si="11"/>
         <v>133328.57142857142</v>
       </c>
-      <c r="M42" s="33">
-        <f t="shared" si="8"/>
+      <c r="O42" s="33">
+        <f t="shared" si="10"/>
         <v>1333.2857142857142</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="C43" s="19" t="s">
@@ -3733,25 +3958,27 @@
       <c r="H43" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="21">
         <v>163404</v>
       </c>
-      <c r="K43" s="21">
-        <f t="shared" si="7"/>
+      <c r="M43" s="21">
+        <f t="shared" si="9"/>
         <v>17507.571428571428</v>
       </c>
-      <c r="L43" s="27">
-        <f t="shared" si="9"/>
+      <c r="N43" s="27">
+        <f t="shared" si="11"/>
         <v>145896.42857142858</v>
       </c>
-      <c r="M43" s="33">
-        <f t="shared" si="8"/>
+      <c r="O43" s="33">
+        <f t="shared" si="10"/>
         <v>1458.9642857142858</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>11</v>
       </c>
       <c r="C44" s="19" t="s">
@@ -3770,25 +3997,27 @@
       <c r="H44" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="21">
         <v>191808</v>
       </c>
-      <c r="K44" s="21">
-        <f t="shared" si="7"/>
+      <c r="M44" s="21">
+        <f t="shared" si="9"/>
         <v>20550.857142857145</v>
       </c>
-      <c r="L44" s="27">
-        <f t="shared" si="9"/>
+      <c r="N44" s="27">
+        <f t="shared" si="11"/>
         <v>171257.14285714284</v>
       </c>
-      <c r="M44" s="33">
-        <f t="shared" si="8"/>
+      <c r="O44" s="33">
+        <f t="shared" si="10"/>
         <v>1712.5714285714287</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="C45" s="19" t="s">
@@ -3807,25 +4036,27 @@
       <c r="H45" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="21">
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="21">
         <v>204888</v>
       </c>
-      <c r="K45" s="21">
-        <f t="shared" si="7"/>
+      <c r="M45" s="21">
+        <f t="shared" si="9"/>
         <v>21952.285714285714</v>
       </c>
-      <c r="L45" s="27">
-        <f t="shared" si="9"/>
+      <c r="N45" s="27">
+        <f t="shared" si="11"/>
         <v>182935.71428571429</v>
       </c>
-      <c r="M45" s="33">
-        <f t="shared" si="8"/>
+      <c r="O45" s="33">
+        <f t="shared" si="10"/>
         <v>1829.3571428571429</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="C46" s="19" t="s">
@@ -3844,25 +4075,27 @@
       <c r="H46" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I46" s="21">
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="21">
         <v>91656</v>
       </c>
-      <c r="K46" s="21">
-        <f t="shared" si="7"/>
+      <c r="M46" s="21">
+        <f t="shared" si="9"/>
         <v>9820.2857142857138</v>
       </c>
-      <c r="L46" s="27">
-        <f t="shared" si="9"/>
+      <c r="N46" s="27">
+        <f t="shared" si="11"/>
         <v>81835.71428571429</v>
       </c>
-      <c r="M46" s="33">
-        <f t="shared" si="8"/>
+      <c r="O46" s="33">
+        <f t="shared" si="10"/>
         <v>818.35714285714289</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="C47" s="19" t="s">
@@ -3881,25 +4114,27 @@
       <c r="H47" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I47" s="21">
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="21">
         <v>203796</v>
       </c>
-      <c r="K47" s="21">
-        <f t="shared" si="7"/>
+      <c r="M47" s="21">
+        <f t="shared" si="9"/>
         <v>21835.285714285714</v>
       </c>
-      <c r="L47" s="27">
-        <f t="shared" si="9"/>
+      <c r="N47" s="27">
+        <f t="shared" si="11"/>
         <v>181960.71428571429</v>
       </c>
-      <c r="M47" s="33">
-        <f t="shared" si="8"/>
+      <c r="O47" s="33">
+        <f t="shared" si="10"/>
         <v>1819.6071428571429</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="C48" s="19" t="s">
@@ -3918,25 +4153,27 @@
       <c r="H48" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="21">
         <v>143856</v>
       </c>
-      <c r="K48" s="21">
-        <f t="shared" si="7"/>
+      <c r="M48" s="21">
+        <f t="shared" si="9"/>
         <v>15413.142857142855</v>
       </c>
-      <c r="L48" s="27">
-        <f t="shared" si="9"/>
+      <c r="N48" s="27">
+        <f t="shared" si="11"/>
         <v>128442.85714285714</v>
       </c>
-      <c r="M48" s="33">
-        <f t="shared" si="8"/>
+      <c r="O48" s="33">
+        <f t="shared" si="10"/>
         <v>1284.4285714285713</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
       <c r="C49" s="19" t="s">
@@ -3955,26 +4192,28 @@
       <c r="H49" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I49" s="21">
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="21">
         <f>11988+10656+95904</f>
         <v>118548</v>
       </c>
-      <c r="K49" s="21">
-        <f t="shared" si="7"/>
+      <c r="M49" s="21">
+        <f t="shared" si="9"/>
         <v>12701.571428571429</v>
       </c>
-      <c r="L49" s="27">
-        <f t="shared" si="9"/>
+      <c r="N49" s="27">
+        <f t="shared" si="11"/>
         <v>105846.42857142857</v>
       </c>
-      <c r="M49" s="33">
-        <f t="shared" si="8"/>
+      <c r="O49" s="33">
+        <f t="shared" si="10"/>
         <v>1058.4642857142858</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>17</v>
       </c>
       <c r="C50" s="19"/>
@@ -3989,23 +4228,25 @@
       <c r="H50" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I50" s="21"/>
-      <c r="K50" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="27">
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="21"/>
+      <c r="M50" s="21">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M50" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N50" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="33">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>18</v>
       </c>
       <c r="C51" s="19"/>
@@ -4020,23 +4261,25 @@
       <c r="H51" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I51" s="21"/>
-      <c r="K51" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="27">
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="21"/>
+      <c r="M51" s="21">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M51" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O51" s="33">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>19</v>
       </c>
       <c r="C52" s="19"/>
@@ -4051,23 +4294,25 @@
       <c r="H52" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I52" s="21"/>
-      <c r="K52" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L52" s="27">
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="21"/>
+      <c r="M52" s="21">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M52" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N52" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O52" s="33">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="C53" s="19"/>
@@ -4082,23 +4327,25 @@
       <c r="H53" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I53" s="21"/>
-      <c r="K53" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="27">
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="21"/>
+      <c r="M53" s="21">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M53" s="33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N53" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O53" s="33">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
       <c r="C54" s="19"/>
@@ -4113,37 +4360,39 @@
       <c r="H54" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I54" s="21"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
       <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="33"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I55" s="44">
-        <f>SUM(I34:I54)</f>
-        <v>2727372</v>
-      </c>
-      <c r="J55" s="44">
-        <f ca="1">SUM(J34:J58)</f>
-        <v>0</v>
-      </c>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="33"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
+        <v>2727372</v>
+      </c>
+      <c r="L55" s="44">
+        <f ca="1">SUM(L34:L58)</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="44">
+        <f>SUM(M34:M54)</f>
         <v>292218.42857142858</v>
       </c>
-      <c r="L55" s="44">
-        <f>SUM(L34:L54)</f>
+      <c r="N55" s="44">
+        <f>SUM(N34:N54)</f>
         <v>2435153.5714285714</v>
       </c>
-      <c r="M55" s="45">
-        <f>SUM(M34:M54)</f>
+      <c r="O55" s="45">
+        <f>SUM(O34:O54)</f>
         <v>24351.535714285714</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M56" s="34"/>
-    </row>
-    <row r="57" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O56" s="34"/>
+    </row>
+    <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C57" s="41" t="s">
         <v>83</v>
       </c>
@@ -4155,11 +4404,13 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="28"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="28"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
@@ -4167,11 +4418,13 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
       <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="30"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="30"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -4180,16 +4433,22 @@
         <v>2</v>
       </c>
       <c r="H59" s="9"/>
-      <c r="I59" s="10" t="s">
+      <c r="I59" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K59" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10" t="s">
+      <c r="M59" s="10"/>
+      <c r="N59" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="31"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O59" s="31"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -4211,20 +4470,26 @@
       <c r="H60" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I60" s="10" t="s">
+      <c r="I60" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K60" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="M60" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L60" s="10" t="s">
+      <c r="N60" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M60" s="32">
+      <c r="O60" s="32">
         <v>2307</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1</v>
       </c>
@@ -4244,23 +4509,25 @@
       <c r="H61" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I61" s="21">
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="21">
         <v>33804</v>
       </c>
-      <c r="K61" s="21">
-        <f t="shared" ref="K61:K80" si="11">M61*12</f>
+      <c r="M61" s="21">
+        <f t="shared" ref="M61:M80" si="13">O61*12</f>
         <v>3621.8571428571427</v>
       </c>
-      <c r="L61" s="27">
-        <f>I61-K61</f>
+      <c r="N61" s="27">
+        <f>K61-M61</f>
         <v>30182.142857142859</v>
       </c>
-      <c r="M61" s="33">
-        <f t="shared" ref="M61:M80" si="12">I61/112</f>
+      <c r="O61" s="33">
+        <f t="shared" ref="O61:O80" si="14">K61/112</f>
         <v>301.82142857142856</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
         <f>A61+1</f>
         <v>2</v>
@@ -4281,25 +4548,27 @@
       <c r="H62" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I62" s="21">
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="21">
         <v>11340</v>
       </c>
-      <c r="K62" s="21">
-        <f t="shared" si="11"/>
+      <c r="M62" s="21">
+        <f t="shared" si="13"/>
         <v>1215</v>
       </c>
-      <c r="L62" s="27">
-        <f t="shared" ref="L62:L80" si="13">I62-K62</f>
+      <c r="N62" s="27">
+        <f t="shared" ref="N62:N80" si="15">K62-M62</f>
         <v>10125</v>
       </c>
-      <c r="M62" s="33">
-        <f t="shared" si="12"/>
+      <c r="O62" s="33">
+        <f t="shared" si="14"/>
         <v>101.25</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
-        <f t="shared" ref="A63:A81" si="14">A62+1</f>
+        <f t="shared" ref="A63:A81" si="16">A62+1</f>
         <v>3</v>
       </c>
       <c r="C63" s="19">
@@ -4318,25 +4587,27 @@
       <c r="H63" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I63" s="21">
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="21">
         <v>5670</v>
       </c>
-      <c r="K63" s="21">
-        <f t="shared" si="11"/>
+      <c r="M63" s="21">
+        <f t="shared" si="13"/>
         <v>607.5</v>
       </c>
-      <c r="L63" s="27">
-        <f t="shared" si="13"/>
+      <c r="N63" s="27">
+        <f t="shared" si="15"/>
         <v>5062.5</v>
       </c>
-      <c r="M63" s="33">
-        <f t="shared" si="12"/>
+      <c r="O63" s="33">
+        <f t="shared" si="14"/>
         <v>50.625</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="C64" s="19">
@@ -4355,25 +4626,27 @@
       <c r="H64" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I64" s="21">
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="21">
         <v>5616</v>
       </c>
-      <c r="K64" s="21">
-        <f t="shared" si="11"/>
+      <c r="M64" s="21">
+        <f t="shared" si="13"/>
         <v>601.71428571428578</v>
       </c>
-      <c r="L64" s="27">
-        <f t="shared" si="13"/>
+      <c r="N64" s="27">
+        <f t="shared" si="15"/>
         <v>5014.2857142857138</v>
       </c>
-      <c r="M64" s="33">
-        <f t="shared" si="12"/>
+      <c r="O64" s="33">
+        <f t="shared" si="14"/>
         <v>50.142857142857146</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="C65" s="19" t="s">
@@ -4392,25 +4665,27 @@
       <c r="H65" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I65" s="21">
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="21">
         <v>11286</v>
       </c>
-      <c r="K65" s="21">
-        <f t="shared" si="11"/>
+      <c r="M65" s="21">
+        <f t="shared" si="13"/>
         <v>1209.2142857142858</v>
       </c>
-      <c r="L65" s="27">
-        <f t="shared" si="13"/>
+      <c r="N65" s="27">
+        <f t="shared" si="15"/>
         <v>10076.785714285714</v>
       </c>
-      <c r="M65" s="33">
-        <f t="shared" si="12"/>
+      <c r="O65" s="33">
+        <f t="shared" si="14"/>
         <v>100.76785714285714</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="C66" s="19" t="s">
@@ -4429,25 +4704,27 @@
       <c r="H66" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I66" s="21">
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="21">
         <v>5616</v>
       </c>
-      <c r="K66" s="21">
-        <f t="shared" si="11"/>
+      <c r="M66" s="21">
+        <f t="shared" si="13"/>
         <v>601.71428571428578</v>
       </c>
-      <c r="L66" s="27">
-        <f t="shared" si="13"/>
+      <c r="N66" s="27">
+        <f t="shared" si="15"/>
         <v>5014.2857142857138</v>
       </c>
-      <c r="M66" s="33">
-        <f t="shared" si="12"/>
+      <c r="O66" s="33">
+        <f t="shared" si="14"/>
         <v>50.142857142857146</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>7</v>
       </c>
       <c r="C67" s="19" t="s">
@@ -4466,25 +4743,27 @@
       <c r="H67" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I67" s="21">
+      <c r="I67" s="20"/>
+      <c r="J67" s="20"/>
+      <c r="K67" s="21">
         <v>5616</v>
       </c>
-      <c r="K67" s="21">
-        <f t="shared" si="11"/>
+      <c r="M67" s="21">
+        <f t="shared" si="13"/>
         <v>601.71428571428578</v>
       </c>
-      <c r="L67" s="27">
-        <f t="shared" si="13"/>
+      <c r="N67" s="27">
+        <f t="shared" si="15"/>
         <v>5014.2857142857138</v>
       </c>
-      <c r="M67" s="33">
-        <f t="shared" si="12"/>
+      <c r="O67" s="33">
+        <f t="shared" si="14"/>
         <v>50.142857142857146</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>8</v>
       </c>
       <c r="C68" s="19" t="s">
@@ -4503,25 +4782,27 @@
       <c r="H68" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I68" s="21">
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="21">
         <v>5670</v>
       </c>
-      <c r="K68" s="21">
-        <f t="shared" si="11"/>
+      <c r="M68" s="21">
+        <f t="shared" si="13"/>
         <v>607.5</v>
       </c>
-      <c r="L68" s="27">
-        <f t="shared" si="13"/>
+      <c r="N68" s="27">
+        <f t="shared" si="15"/>
         <v>5062.5</v>
       </c>
-      <c r="M68" s="33">
-        <f t="shared" si="12"/>
+      <c r="O68" s="33">
+        <f t="shared" si="14"/>
         <v>50.625</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="C69" s="19" t="s">
@@ -4540,25 +4821,27 @@
       <c r="H69" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I69" s="21">
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="21">
         <v>5616</v>
       </c>
-      <c r="K69" s="21">
-        <f t="shared" si="11"/>
+      <c r="M69" s="21">
+        <f t="shared" si="13"/>
         <v>601.71428571428578</v>
       </c>
-      <c r="L69" s="27">
-        <f t="shared" si="13"/>
+      <c r="N69" s="27">
+        <f t="shared" si="15"/>
         <v>5014.2857142857138</v>
       </c>
-      <c r="M69" s="33">
-        <f t="shared" si="12"/>
+      <c r="O69" s="33">
+        <f t="shared" si="14"/>
         <v>50.142857142857146</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="C70" s="19"/>
@@ -4573,23 +4856,25 @@
       <c r="H70" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I70" s="21"/>
-      <c r="K70" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L70" s="27">
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="21"/>
+      <c r="M70" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M70" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N70" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O70" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="C71" s="19"/>
@@ -4604,23 +4889,25 @@
       <c r="H71" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I71" s="21"/>
-      <c r="K71" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L71" s="27">
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="21"/>
+      <c r="M71" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M71" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N71" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O71" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="C72" s="19"/>
@@ -4635,23 +4922,25 @@
       <c r="H72" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I72" s="21"/>
-      <c r="K72" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L72" s="27">
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="21"/>
+      <c r="M72" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M72" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N72" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O72" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
       <c r="C73" s="19"/>
@@ -4666,23 +4955,25 @@
       <c r="H73" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I73" s="21"/>
-      <c r="K73" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L73" s="27">
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="21"/>
+      <c r="M73" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M73" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N73" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O73" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="C74" s="19"/>
@@ -4697,23 +4988,25 @@
       <c r="H74" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I74" s="21"/>
-      <c r="K74" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L74" s="27">
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="21"/>
+      <c r="M74" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M74" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N74" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O74" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="C75" s="19"/>
@@ -4728,23 +5021,25 @@
       <c r="H75" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I75" s="21"/>
-      <c r="K75" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L75" s="27">
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="21"/>
+      <c r="M75" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M75" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N75" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O75" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="C76" s="19"/>
@@ -4759,23 +5054,25 @@
       <c r="H76" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I76" s="21"/>
-      <c r="K76" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L76" s="27">
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+      <c r="K76" s="21"/>
+      <c r="M76" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M76" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N76" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O76" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>17</v>
       </c>
       <c r="C77" s="19"/>
@@ -4790,23 +5087,25 @@
       <c r="H77" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I77" s="21"/>
-      <c r="K77" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L77" s="27">
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="21"/>
+      <c r="M77" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M77" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N77" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O77" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="C78" s="19"/>
@@ -4821,23 +5120,25 @@
       <c r="H78" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I78" s="21"/>
-      <c r="K78" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L78" s="27">
+      <c r="I78" s="20"/>
+      <c r="J78" s="20"/>
+      <c r="K78" s="21"/>
+      <c r="M78" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M78" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N78" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O78" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>19</v>
       </c>
       <c r="C79" s="19"/>
@@ -4852,23 +5153,25 @@
       <c r="H79" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I79" s="21"/>
-      <c r="K79" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L79" s="27">
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="21"/>
+      <c r="M79" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M79" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N79" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O79" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="C80" s="19"/>
@@ -4883,23 +5186,25 @@
       <c r="H80" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I80" s="21"/>
-      <c r="K80" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L80" s="27">
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
+      <c r="K80" s="21"/>
+      <c r="M80" s="21">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M80" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N80" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O80" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>21</v>
       </c>
       <c r="C81" s="19"/>
@@ -4914,34 +5219,36 @@
       <c r="H81" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I81" s="21"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
       <c r="K81" s="21"/>
-      <c r="L81" s="21"/>
-      <c r="M81" s="33"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I82" s="44">
-        <f>SUM(I61:I81)</f>
-        <v>90234</v>
-      </c>
-      <c r="J82" s="44">
-        <f ca="1">SUM(J61:J85)</f>
-        <v>0</v>
-      </c>
+      <c r="M81" s="21"/>
+      <c r="N81" s="21"/>
+      <c r="O81" s="33"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
+        <v>90234</v>
+      </c>
+      <c r="L82" s="44">
+        <f ca="1">SUM(L61:L85)</f>
+        <v>0</v>
+      </c>
+      <c r="M82" s="44">
+        <f>SUM(M61:M81)</f>
         <v>9667.9285714285743</v>
       </c>
-      <c r="L82" s="44">
-        <f>SUM(L61:L81)</f>
+      <c r="N82" s="44">
+        <f>SUM(N61:N81)</f>
         <v>80566.071428571406</v>
       </c>
-      <c r="M82" s="45">
-        <f>SUM(M61:M81)</f>
+      <c r="O82" s="45">
+        <f>SUM(O61:O81)</f>
         <v>805.66071428571422</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C84" s="41" t="s">
         <v>102</v>
       </c>
@@ -4953,11 +5260,13 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
-      <c r="M84" s="28"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="O84" s="28"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
@@ -4965,11 +5274,13 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
       <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
       <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="30"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M85" s="8"/>
+      <c r="N85" s="8"/>
+      <c r="O85" s="30"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -4978,16 +5289,22 @@
         <v>2</v>
       </c>
       <c r="H86" s="9"/>
-      <c r="K86" s="10" t="s">
+      <c r="I86" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M86" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10" t="s">
+      <c r="N86" s="10"/>
+      <c r="O86" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N86" s="31"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P86" s="31"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>73</v>
       </c>
@@ -5009,23 +5326,29 @@
       <c r="H87" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I87" s="46" t="s">
+      <c r="I87" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K87" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="K87" s="10" t="s">
+      <c r="M87" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L87" s="10" t="s">
+      <c r="N87" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M87" s="10" t="s">
+      <c r="O87" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N87" s="32">
+      <c r="P87" s="32">
         <v>2307</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1</v>
       </c>
@@ -5045,27 +5368,29 @@
       <c r="H88" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I88" s="21">
+      <c r="I88" s="20"/>
+      <c r="J88" s="20"/>
+      <c r="K88" s="21">
         <v>1608</v>
       </c>
-      <c r="J88" s="21"/>
-      <c r="K88" s="21">
+      <c r="L88" s="21"/>
+      <c r="M88" s="21">
         <v>16488</v>
       </c>
-      <c r="L88" s="21">
-        <f t="shared" ref="L88:L107" si="15">N88*12</f>
+      <c r="N88" s="21">
+        <f t="shared" ref="N88:N107" si="17">P88*12</f>
         <v>1766.5714285714287</v>
       </c>
-      <c r="M88" s="27">
-        <f t="shared" ref="M88:M107" si="16">K88-L88</f>
+      <c r="O88" s="27">
+        <f t="shared" ref="O88:O107" si="18">M88-N88</f>
         <v>14721.428571428571</v>
       </c>
-      <c r="N88" s="33">
-        <f t="shared" ref="N88:N107" si="17">K88/112</f>
+      <c r="P88" s="33">
+        <f t="shared" ref="P88:P107" si="19">M88/112</f>
         <v>147.21428571428572</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89">
         <f>A88+1</f>
         <v>2</v>
@@ -5086,29 +5411,31 @@
       <c r="H89" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I89" s="21">
+      <c r="I89" s="20"/>
+      <c r="J89" s="20"/>
+      <c r="K89" s="21">
         <v>1849</v>
       </c>
-      <c r="J89" s="21"/>
-      <c r="K89" s="21">
+      <c r="L89" s="21"/>
+      <c r="M89" s="21">
         <v>11328</v>
       </c>
-      <c r="L89" s="21">
-        <f t="shared" si="15"/>
+      <c r="N89" s="21">
+        <f t="shared" si="17"/>
         <v>1213.7142857142858</v>
       </c>
-      <c r="M89" s="27">
-        <f t="shared" si="16"/>
+      <c r="O89" s="27">
+        <f t="shared" si="18"/>
         <v>10114.285714285714</v>
       </c>
-      <c r="N89" s="33">
-        <f t="shared" si="17"/>
+      <c r="P89" s="33">
+        <f t="shared" si="19"/>
         <v>101.14285714285714</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90">
-        <f t="shared" ref="A90:A108" si="18">A89+1</f>
+        <f t="shared" ref="A90:A108" si="20">A89+1</f>
         <v>3</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -5127,29 +5454,31 @@
       <c r="H90" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I90" s="21">
+      <c r="I90" s="20"/>
+      <c r="J90" s="20"/>
+      <c r="K90" s="21">
         <v>1836</v>
       </c>
-      <c r="J90" s="21"/>
-      <c r="K90" s="21">
+      <c r="L90" s="21"/>
+      <c r="M90" s="21">
         <v>11016</v>
       </c>
-      <c r="L90" s="21">
-        <f t="shared" si="15"/>
+      <c r="N90" s="21">
+        <f t="shared" si="17"/>
         <v>1180.2857142857142</v>
       </c>
-      <c r="M90" s="27">
-        <f t="shared" si="16"/>
+      <c r="O90" s="27">
+        <f t="shared" si="18"/>
         <v>9835.7142857142862</v>
       </c>
-      <c r="N90" s="33">
-        <f t="shared" si="17"/>
+      <c r="P90" s="33">
+        <f t="shared" si="19"/>
         <v>98.357142857142861</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="C91" s="19" t="s">
@@ -5168,29 +5497,31 @@
       <c r="H91" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I91" s="21">
+      <c r="I91" s="20"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="21">
         <v>1709</v>
       </c>
-      <c r="J91" s="21"/>
-      <c r="K91" s="21">
+      <c r="L91" s="21"/>
+      <c r="M91" s="21">
         <v>13800</v>
       </c>
-      <c r="L91" s="21">
-        <f t="shared" si="15"/>
+      <c r="N91" s="21">
+        <f t="shared" si="17"/>
         <v>1478.5714285714284</v>
       </c>
-      <c r="M91" s="27">
-        <f t="shared" si="16"/>
+      <c r="O91" s="27">
+        <f t="shared" si="18"/>
         <v>12321.428571428572</v>
       </c>
-      <c r="N91" s="33">
-        <f t="shared" si="17"/>
+      <c r="P91" s="33">
+        <f t="shared" si="19"/>
         <v>123.21428571428571</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="C92" s="19" t="s">
@@ -5209,29 +5540,31 @@
       <c r="H92" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I92" s="21">
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+      <c r="K92" s="21">
         <v>1836</v>
       </c>
-      <c r="J92" s="21"/>
-      <c r="K92" s="21">
+      <c r="L92" s="21"/>
+      <c r="M92" s="21">
         <v>11016</v>
       </c>
-      <c r="L92" s="21">
-        <f t="shared" si="15"/>
+      <c r="N92" s="21">
+        <f t="shared" si="17"/>
         <v>1180.2857142857142</v>
       </c>
-      <c r="M92" s="27">
-        <f t="shared" si="16"/>
+      <c r="O92" s="27">
+        <f t="shared" si="18"/>
         <v>9835.7142857142862</v>
       </c>
-      <c r="N92" s="33">
-        <f t="shared" si="17"/>
+      <c r="P92" s="33">
+        <f t="shared" si="19"/>
         <v>98.357142857142861</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6</v>
       </c>
       <c r="C93" s="19" t="s">
@@ -5250,29 +5583,31 @@
       <c r="H93" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I93" s="21">
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
+      <c r="K93" s="21">
         <v>1836</v>
       </c>
-      <c r="J93" s="21"/>
-      <c r="K93" s="21">
+      <c r="L93" s="21"/>
+      <c r="M93" s="21">
         <v>11016</v>
       </c>
-      <c r="L93" s="21">
-        <f t="shared" si="15"/>
+      <c r="N93" s="21">
+        <f t="shared" si="17"/>
         <v>1180.2857142857142</v>
       </c>
-      <c r="M93" s="27">
-        <f t="shared" si="16"/>
+      <c r="O93" s="27">
+        <f t="shared" si="18"/>
         <v>9835.7142857142862</v>
       </c>
-      <c r="N93" s="33">
-        <f t="shared" si="17"/>
+      <c r="P93" s="33">
+        <f t="shared" si="19"/>
         <v>98.357142857142861</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="C94" s="19"/>
@@ -5287,25 +5622,27 @@
       <c r="H94" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I94" s="21"/>
-      <c r="J94" s="21"/>
+      <c r="I94" s="20"/>
+      <c r="J94" s="20"/>
       <c r="K94" s="21"/>
-      <c r="L94" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N94" s="33">
+      <c r="L94" s="21"/>
+      <c r="M94" s="21"/>
+      <c r="N94" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O94" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P94" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
       <c r="C95" s="19"/>
@@ -5320,25 +5657,27 @@
       <c r="H95" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I95" s="21"/>
-      <c r="J95" s="21"/>
+      <c r="I95" s="20"/>
+      <c r="J95" s="20"/>
       <c r="K95" s="21"/>
-      <c r="L95" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M95" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N95" s="33">
+      <c r="L95" s="21"/>
+      <c r="M95" s="21"/>
+      <c r="N95" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O95" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P95" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="C96" s="19"/>
@@ -5353,25 +5692,27 @@
       <c r="H96" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I96" s="21"/>
-      <c r="J96" s="21"/>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
       <c r="K96" s="21"/>
-      <c r="L96" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N96" s="33">
+      <c r="L96" s="21"/>
+      <c r="M96" s="21"/>
+      <c r="N96" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O96" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P96" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="C97" s="19"/>
@@ -5386,25 +5727,27 @@
       <c r="H97" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I97" s="21"/>
-      <c r="J97" s="21"/>
+      <c r="I97" s="20"/>
+      <c r="J97" s="20"/>
       <c r="K97" s="21"/>
-      <c r="L97" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M97" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N97" s="33">
+      <c r="L97" s="21"/>
+      <c r="M97" s="21"/>
+      <c r="N97" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O97" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P97" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11</v>
       </c>
       <c r="C98" s="19"/>
@@ -5419,25 +5762,27 @@
       <c r="H98" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I98" s="21"/>
-      <c r="J98" s="21"/>
+      <c r="I98" s="20"/>
+      <c r="J98" s="20"/>
       <c r="K98" s="21"/>
-      <c r="L98" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M98" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N98" s="33">
+      <c r="L98" s="21"/>
+      <c r="M98" s="21"/>
+      <c r="N98" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O98" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P98" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>12</v>
       </c>
       <c r="C99" s="19"/>
@@ -5452,25 +5797,27 @@
       <c r="H99" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I99" s="21"/>
-      <c r="J99" s="21"/>
+      <c r="I99" s="20"/>
+      <c r="J99" s="20"/>
       <c r="K99" s="21"/>
-      <c r="L99" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M99" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N99" s="33">
+      <c r="L99" s="21"/>
+      <c r="M99" s="21"/>
+      <c r="N99" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O99" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P99" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>13</v>
       </c>
       <c r="C100" s="19"/>
@@ -5485,25 +5832,27 @@
       <c r="H100" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I100" s="21"/>
-      <c r="J100" s="21"/>
+      <c r="I100" s="20"/>
+      <c r="J100" s="20"/>
       <c r="K100" s="21"/>
-      <c r="L100" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M100" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N100" s="33">
+      <c r="L100" s="21"/>
+      <c r="M100" s="21"/>
+      <c r="N100" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O100" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P100" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="C101" s="19"/>
@@ -5518,25 +5867,27 @@
       <c r="H101" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I101" s="21"/>
-      <c r="J101" s="21"/>
+      <c r="I101" s="20"/>
+      <c r="J101" s="20"/>
       <c r="K101" s="21"/>
-      <c r="L101" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M101" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N101" s="33">
+      <c r="L101" s="21"/>
+      <c r="M101" s="21"/>
+      <c r="N101" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O101" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P101" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>15</v>
       </c>
       <c r="C102" s="19"/>
@@ -5551,25 +5902,27 @@
       <c r="H102" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I102" s="21"/>
-      <c r="J102" s="21"/>
+      <c r="I102" s="20"/>
+      <c r="J102" s="20"/>
       <c r="K102" s="21"/>
-      <c r="L102" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M102" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N102" s="33">
+      <c r="L102" s="21"/>
+      <c r="M102" s="21"/>
+      <c r="N102" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O102" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P102" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>16</v>
       </c>
       <c r="C103" s="19"/>
@@ -5584,25 +5937,27 @@
       <c r="H103" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I103" s="21"/>
-      <c r="J103" s="21"/>
+      <c r="I103" s="20"/>
+      <c r="J103" s="20"/>
       <c r="K103" s="21"/>
-      <c r="L103" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M103" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N103" s="33">
+      <c r="L103" s="21"/>
+      <c r="M103" s="21"/>
+      <c r="N103" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O103" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P103" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>17</v>
       </c>
       <c r="C104" s="19"/>
@@ -5617,25 +5972,27 @@
       <c r="H104" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I104" s="21"/>
-      <c r="J104" s="21"/>
+      <c r="I104" s="20"/>
+      <c r="J104" s="20"/>
       <c r="K104" s="21"/>
-      <c r="L104" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N104" s="33">
+      <c r="L104" s="21"/>
+      <c r="M104" s="21"/>
+      <c r="N104" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O104" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P104" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>18</v>
       </c>
       <c r="C105" s="19"/>
@@ -5650,25 +6007,27 @@
       <c r="H105" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I105" s="21"/>
-      <c r="J105" s="21"/>
+      <c r="I105" s="20"/>
+      <c r="J105" s="20"/>
       <c r="K105" s="21"/>
-      <c r="L105" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N105" s="33">
+      <c r="L105" s="21"/>
+      <c r="M105" s="21"/>
+      <c r="N105" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O105" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P105" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19</v>
       </c>
       <c r="C106" s="19"/>
@@ -5683,25 +6042,27 @@
       <c r="H106" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I106" s="21"/>
-      <c r="J106" s="21"/>
+      <c r="I106" s="20"/>
+      <c r="J106" s="20"/>
       <c r="K106" s="21"/>
-      <c r="L106" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M106" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N106" s="33">
+      <c r="L106" s="21"/>
+      <c r="M106" s="21"/>
+      <c r="N106" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O106" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P106" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="C107" s="19"/>
@@ -5716,25 +6077,27 @@
       <c r="H107" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
+      <c r="I107" s="20"/>
+      <c r="J107" s="20"/>
       <c r="K107" s="21"/>
-      <c r="L107" s="21">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="27">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N107" s="33">
+      <c r="L107" s="21"/>
+      <c r="M107" s="21"/>
+      <c r="N107" s="21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O107" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P107" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="C108" s="19"/>
@@ -5749,36 +6112,38 @@
       <c r="H108" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I108" s="21"/>
-      <c r="J108" s="21"/>
+      <c r="I108" s="20"/>
+      <c r="J108" s="20"/>
       <c r="K108" s="21"/>
       <c r="L108" s="21"/>
       <c r="M108" s="21"/>
-      <c r="N108" s="33"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I109" s="44">
-        <f>SUM(I88:I108)</f>
-        <v>10674</v>
-      </c>
-      <c r="J109" s="44">
-        <f ca="1">SUM(J88:J112)</f>
-        <v>0</v>
-      </c>
+      <c r="N108" s="21"/>
+      <c r="O108" s="21"/>
+      <c r="P108" s="33"/>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K109" s="44">
         <f>SUM(K88:K108)</f>
+        <v>10674</v>
+      </c>
+      <c r="L109" s="44">
+        <f ca="1">SUM(L88:L112)</f>
+        <v>0</v>
+      </c>
+      <c r="M109" s="44">
+        <f>SUM(M88:M108)</f>
         <v>74664</v>
       </c>
-      <c r="L109" s="44">
-        <f>SUM(L88:L108)</f>
+      <c r="N109" s="44">
+        <f>SUM(N88:N108)</f>
         <v>7999.7142857142862</v>
       </c>
-      <c r="M109" s="45">
-        <f>SUM(M88:M108)</f>
+      <c r="O109" s="45">
+        <f>SUM(O88:O108)</f>
         <v>66664.28571428571</v>
       </c>
-      <c r="N109" s="45">
-        <f>SUM(N88:N108)</f>
+      <c r="P109" s="45">
+        <f>SUM(P88:P108)</f>
         <v>666.64285714285722</v>
       </c>
     </row>

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BB822-D589-4B0B-9CAD-E2A6DF7E407A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB68953-BAD7-47C7-B52E-E9552F295811}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="121">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -390,6 +390,12 @@
   </si>
   <si>
     <t>06/27/2026</t>
+  </si>
+  <si>
+    <t>06/29/2026</t>
+  </si>
+  <si>
+    <t>06/29/2029</t>
   </si>
 </sst>
 </file>
@@ -3064,7 +3070,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="19" t="s">
+        <v>119</v>
+      </c>
       <c r="D18" s="20" t="s">
         <v>68</v>
       </c>
@@ -3072,27 +3080,33 @@
       <c r="F18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="20">
+        <v>518776542</v>
+      </c>
       <c r="H18" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
+      <c r="I18" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J18" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K18" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M18" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N18" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O18" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -3104,7 +3118,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>119</v>
+      </c>
       <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
@@ -3112,27 +3128,33 @@
       <c r="F19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="20">
+        <v>518776527</v>
+      </c>
       <c r="H19" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
+      <c r="I19" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J19" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K19" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M19" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N19" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O19" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -3144,7 +3166,9 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="19" t="s">
+        <v>119</v>
+      </c>
       <c r="D20" s="20" t="s">
         <v>68</v>
       </c>
@@ -3152,27 +3176,33 @@
       <c r="F20" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="20"/>
+      <c r="G20" s="20">
+        <v>518776728</v>
+      </c>
       <c r="H20" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
+      <c r="I20" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J20" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K20" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M20" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N20" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O20" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3184,7 +3214,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C21" s="19"/>
+      <c r="C21" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D21" s="20" t="s">
         <v>68</v>
       </c>
@@ -3192,27 +3224,33 @@
       <c r="F21" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="20">
+        <v>518776229</v>
+      </c>
       <c r="H21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
+      <c r="I21" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J21" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K21" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M21" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N21" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O21" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -3459,15 +3497,15 @@
       <c r="G28"/>
       <c r="I28" s="44">
         <f t="shared" ref="I28:J28" si="8">SUM(I7:I27)</f>
-        <v>15009679</v>
+        <v>20598463</v>
       </c>
       <c r="J28" s="44">
         <f t="shared" si="8"/>
-        <v>887994.66000000015</v>
+        <v>1131374.8200000003</v>
       </c>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>14121684.340000004</v>
+        <v>19467088.180000007</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3475,15 +3513,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>1513037.6078571428</v>
+        <v>2085759.4478571427</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>12608646.732142858</v>
+        <v>17381328.732142858</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>126086.46732142857</v>
+        <v>173813.28732142854</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/PURCHASES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB68953-BAD7-47C7-B52E-E9552F295811}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AC6845-3237-471F-B5D0-145172FFF4A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="122">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -395,7 +395,10 @@
     <t>06/29/2026</t>
   </si>
   <si>
-    <t>06/29/2029</t>
+    <t>06/30/2026</t>
+  </si>
+  <si>
+    <t>R18</t>
   </si>
 </sst>
 </file>
@@ -2369,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{423D5057-7111-4BE4-94EA-57775A7107A8}">
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
@@ -2611,13 +2614,13 @@
         <v>1206441.4107142857</v>
       </c>
       <c r="O8" s="33">
-        <f t="shared" ref="O8:O26" si="0">K8/112</f>
+        <f t="shared" ref="O8:O28" si="0">K8/112</f>
         <v>12064.414107142857</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" ref="A9:B27" si="1">A8+1</f>
+        <f t="shared" ref="A9:B26" si="1">A8+1</f>
         <v>3</v>
       </c>
       <c r="B9" s="23">
@@ -2653,11 +2656,11 @@
         <v>1336350.96</v>
       </c>
       <c r="M9" s="21">
-        <f t="shared" ref="M9:M26" si="2">O9*12</f>
+        <f t="shared" ref="M9:M28" si="2">O9*12</f>
         <v>143180.46</v>
       </c>
       <c r="N9" s="27">
-        <f t="shared" ref="N9:N26" si="3">K9-M9</f>
+        <f t="shared" ref="N9:N28" si="3">K9-M9</f>
         <v>1193170.5</v>
       </c>
       <c r="O9" s="33">
@@ -3045,7 +3048,7 @@
         <v>60845.04</v>
       </c>
       <c r="K17" s="21">
-        <f t="shared" ref="K17:K27" si="4">I17-J17</f>
+        <f t="shared" ref="K17:K29" si="4">I17-J17</f>
         <v>1336350.96</v>
       </c>
       <c r="M17" s="21">
@@ -3215,7 +3218,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>68</v>
@@ -3262,7 +3265,9 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C22" s="19"/>
+      <c r="C22" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D22" s="20" t="s">
         <v>68</v>
       </c>
@@ -3270,27 +3275,33 @@
       <c r="F22" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="20"/>
+      <c r="G22" s="20">
+        <v>518782222</v>
+      </c>
       <c r="H22" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
+      <c r="I22" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J22" s="21">
+        <v>54419.040000000001</v>
+      </c>
       <c r="K22" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1342776.96</v>
       </c>
       <c r="M22" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143868.96</v>
       </c>
       <c r="N22" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1198908</v>
       </c>
       <c r="O22" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11989.08</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3302,7 +3313,9 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="C23" s="19"/>
+      <c r="C23" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D23" s="20" t="s">
         <v>68</v>
       </c>
@@ -3310,27 +3323,33 @@
       <c r="F23" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="20"/>
+      <c r="G23" s="20">
+        <v>518782262</v>
+      </c>
       <c r="H23" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
+      <c r="I23" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J23" s="21">
+        <v>54419.040000000001</v>
+      </c>
       <c r="K23" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1342776.96</v>
       </c>
       <c r="M23" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143868.96</v>
       </c>
       <c r="N23" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1198908</v>
       </c>
       <c r="O23" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11989.08</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3342,7 +3361,9 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="C24" s="19"/>
+      <c r="C24" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D24" s="20" t="s">
         <v>68</v>
       </c>
@@ -3350,27 +3371,33 @@
       <c r="F24" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="20"/>
+      <c r="G24" s="20">
+        <v>518781966</v>
+      </c>
       <c r="H24" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
+      <c r="I24" s="21">
+        <v>1345788</v>
+      </c>
+      <c r="J24" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K24" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1284942.96</v>
       </c>
       <c r="M24" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>137672.46</v>
       </c>
       <c r="N24" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1147270.5</v>
       </c>
       <c r="O24" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11472.705</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3382,7 +3409,9 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="C25" s="19"/>
+      <c r="C25" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D25" s="20" t="s">
         <v>68</v>
       </c>
@@ -3390,27 +3419,33 @@
       <c r="F25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="20"/>
+      <c r="G25" s="20">
+        <v>518782197</v>
+      </c>
       <c r="H25" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
+      <c r="I25" s="21">
+        <v>382606</v>
+      </c>
+      <c r="J25" s="21">
+        <v>11997.24</v>
+      </c>
       <c r="K25" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>370608.76</v>
       </c>
       <c r="M25" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>39708.08142857143</v>
       </c>
       <c r="N25" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>330900.67857142858</v>
       </c>
       <c r="O25" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3309.0067857142858</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3422,7 +3457,9 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="C26" s="19"/>
+      <c r="C26" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D26" s="20" t="s">
         <v>68</v>
       </c>
@@ -3430,295 +3467,318 @@
       <c r="F26" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="20"/>
+      <c r="G26" s="20">
+        <v>518782145</v>
+      </c>
       <c r="H26" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
+      <c r="I26" s="21">
+        <v>265248</v>
+      </c>
+      <c r="J26" s="21">
+        <v>25136.41</v>
+      </c>
       <c r="K26" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240111.59</v>
       </c>
       <c r="M26" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25726.241785714286</v>
       </c>
       <c r="N26" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>214385.34821428571</v>
       </c>
       <c r="O26" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2143.853482142857</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="23"/>
+      <c r="C27" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="20">
+        <v>518782046</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" s="21">
+        <v>2136888</v>
+      </c>
+      <c r="J27" s="21">
+        <v>93057.12</v>
+      </c>
+      <c r="K27" s="21">
+        <f t="shared" si="4"/>
+        <v>2043830.88</v>
+      </c>
+      <c r="M27" s="21">
+        <f t="shared" si="2"/>
+        <v>218981.87999999998</v>
+      </c>
+      <c r="N27" s="27">
+        <f t="shared" si="3"/>
+        <v>1824849</v>
+      </c>
+      <c r="O27" s="33">
+        <f t="shared" si="0"/>
+        <v>18248.489999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28" s="23"/>
+      <c r="C28" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="20">
+        <v>518782174</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="21">
+        <v>167622</v>
+      </c>
+      <c r="J28" s="21">
+        <v>15047.76</v>
+      </c>
+      <c r="K28" s="21">
+        <f t="shared" si="4"/>
+        <v>152574.24</v>
+      </c>
+      <c r="M28" s="21">
+        <f t="shared" si="2"/>
+        <v>16347.24</v>
+      </c>
+      <c r="N28" s="27">
+        <f t="shared" si="3"/>
+        <v>136227</v>
+      </c>
+      <c r="O28" s="33">
+        <f t="shared" si="0"/>
+        <v>1362.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29" s="23">
         <f>B26+1</f>
         <v>21</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21">
+      <c r="C29" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="20">
+        <v>518782185</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="21">
+        <v>186700</v>
+      </c>
+      <c r="J29" s="21">
+        <v>8401</v>
+      </c>
+      <c r="K29" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="21">
-        <f t="shared" ref="M27" si="5">O27*12</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="27">
-        <f t="shared" ref="N27" si="6">K27-M27</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="33">
-        <f t="shared" ref="O27" si="7">K27/112</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G28"/>
-      <c r="I28" s="44">
-        <f t="shared" ref="I28:J28" si="8">SUM(I7:I27)</f>
-        <v>20598463</v>
-      </c>
-      <c r="J28" s="44">
+        <v>178299</v>
+      </c>
+      <c r="M29" s="21">
+        <f t="shared" ref="M29" si="5">O29*12</f>
+        <v>19103.464285714286</v>
+      </c>
+      <c r="N29" s="27">
+        <f t="shared" ref="N29" si="6">K29-M29</f>
+        <v>159195.53571428571</v>
+      </c>
+      <c r="O29" s="33">
+        <f t="shared" ref="O29" si="7">K29/112</f>
+        <v>1591.9553571428571</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G30"/>
+      <c r="I30" s="44">
+        <f t="shared" ref="I30:J30" si="8">SUM(I7:I29)</f>
+        <v>27877707</v>
+      </c>
+      <c r="J30" s="44">
         <f t="shared" si="8"/>
-        <v>1131374.8200000003</v>
-      </c>
-      <c r="K28" s="44">
-        <f>SUM(K7:K27)</f>
-        <v>19467088.180000007</v>
-      </c>
-      <c r="L28" s="44">
-        <f ca="1">SUM(L7:L31)</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="44">
-        <f>SUM(M7:M27)</f>
-        <v>2085759.4478571427</v>
-      </c>
-      <c r="N28" s="44">
-        <f>SUM(N7:N27)</f>
-        <v>17381328.732142858</v>
-      </c>
-      <c r="O28" s="44">
-        <f>SUM(O7:O27)</f>
-        <v>173813.28732142854</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G29"/>
-      <c r="O29" s="34"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C30" s="41" t="s">
+        <v>1454697.4700000004</v>
+      </c>
+      <c r="K30" s="44">
+        <f>SUM(K7:K29)</f>
+        <v>26423009.530000009</v>
+      </c>
+      <c r="L30" s="44">
+        <f ca="1">SUM(L7:L33)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="44">
+        <f>SUM(M7:M29)</f>
+        <v>2831036.735357143</v>
+      </c>
+      <c r="N30" s="44">
+        <f>SUM(N7:N29)</f>
+        <v>23591972.794642862</v>
+      </c>
+      <c r="O30" s="44">
+        <f>SUM(O7:O29)</f>
+        <v>235919.72794642847</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G31"/>
+      <c r="O31" s="34"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C32" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="43" t="s">
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="28"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="30"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="28"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="30"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9" t="s">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J34" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K34" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10" t="s">
+      <c r="M34" s="10"/>
+      <c r="N34" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="31"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="O34" s="31"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D35" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F35" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G35" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I35" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J35" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="K35" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="M35" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N33" s="10" t="s">
+      <c r="N35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O33" s="32">
+      <c r="O35" s="32">
         <v>2307</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="C34" s="19">
-        <v>46028</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="21">
-        <v>105480</v>
-      </c>
-      <c r="M34" s="21">
-        <f t="shared" ref="M34:M53" si="9">O34*12</f>
-        <v>11301.428571428572</v>
-      </c>
-      <c r="N34" s="27">
-        <f>K34-M34</f>
-        <v>94178.57142857142</v>
-      </c>
-      <c r="O34" s="33">
-        <f t="shared" ref="O34:O53" si="10">K34/112</f>
-        <v>941.78571428571433</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <f>A34+1</f>
-        <v>2</v>
-      </c>
-      <c r="C35" s="19">
-        <v>46240</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="21">
-        <v>199368</v>
-      </c>
-      <c r="M35" s="21">
-        <f t="shared" si="9"/>
-        <v>21360.857142857145</v>
-      </c>
-      <c r="N35" s="27">
-        <f t="shared" ref="N35:N53" si="11">K35-M35</f>
-        <v>178007.14285714284</v>
-      </c>
-      <c r="O35" s="33">
-        <f t="shared" si="10"/>
-        <v>1780.0714285714287</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
-        <f t="shared" ref="A36:A54" si="12">A35+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" s="19">
-        <v>46271</v>
+        <v>46028</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="20"/>
+      <c r="E36" s="12"/>
       <c r="F36" s="20" t="s">
         <v>70</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H36" s="20" t="s">
         <v>74</v>
@@ -3726,28 +3786,28 @@
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
       <c r="K36" s="21">
-        <v>177156</v>
+        <v>105480</v>
       </c>
       <c r="M36" s="21">
-        <f t="shared" si="9"/>
-        <v>18981</v>
+        <f t="shared" ref="M36:M55" si="9">O36*12</f>
+        <v>11301.428571428572</v>
       </c>
       <c r="N36" s="27">
-        <f t="shared" si="11"/>
-        <v>158175</v>
+        <f>K36-M36</f>
+        <v>94178.57142857142</v>
       </c>
       <c r="O36" s="33">
-        <f t="shared" si="10"/>
-        <v>1581.75</v>
+        <f t="shared" ref="O36:O55" si="10">K36/112</f>
+        <v>941.78571428571433</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
-        <f t="shared" si="12"/>
-        <v>4</v>
+        <f>A36+1</f>
+        <v>2</v>
       </c>
       <c r="C37" s="19">
-        <v>46301</v>
+        <v>46240</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>68</v>
@@ -3757,7 +3817,7 @@
         <v>70</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H37" s="20" t="s">
         <v>74</v>
@@ -3765,28 +3825,28 @@
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
       <c r="K37" s="21">
-        <v>203796</v>
+        <v>199368</v>
       </c>
       <c r="M37" s="21">
         <f t="shared" si="9"/>
-        <v>21835.285714285714</v>
+        <v>21360.857142857145</v>
       </c>
       <c r="N37" s="27">
-        <f t="shared" si="11"/>
-        <v>181960.71428571429</v>
+        <f t="shared" ref="N37:N55" si="11">K37-M37</f>
+        <v>178007.14285714284</v>
       </c>
       <c r="O37" s="33">
         <f t="shared" si="10"/>
-        <v>1819.6071428571429</v>
+        <v>1780.0714285714287</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
-        <f t="shared" si="12"/>
-        <v>5</v>
+        <f t="shared" ref="A38:A56" si="12">A37+1</f>
+        <v>3</v>
       </c>
       <c r="C38" s="19">
-        <v>46332</v>
+        <v>46271</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>68</v>
@@ -3796,7 +3856,7 @@
         <v>70</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H38" s="20" t="s">
         <v>74</v>
@@ -3804,28 +3864,28 @@
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
       <c r="K38" s="21">
-        <v>187884</v>
+        <v>177156</v>
       </c>
       <c r="M38" s="21">
         <f t="shared" si="9"/>
-        <v>20130.428571428572</v>
+        <v>18981</v>
       </c>
       <c r="N38" s="27">
         <f t="shared" si="11"/>
-        <v>167753.57142857142</v>
+        <v>158175</v>
       </c>
       <c r="O38" s="33">
         <f t="shared" si="10"/>
-        <v>1677.5357142857142</v>
+        <v>1581.75</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C39" s="19">
-        <v>46332</v>
+        <v>46301</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>68</v>
@@ -3835,7 +3895,7 @@
         <v>70</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H39" s="20" t="s">
         <v>74</v>
@@ -3843,28 +3903,28 @@
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
       <c r="K39" s="21">
-        <v>191808</v>
+        <v>203796</v>
       </c>
       <c r="M39" s="21">
         <f t="shared" si="9"/>
-        <v>20550.857142857145</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N39" s="27">
         <f t="shared" si="11"/>
-        <v>171257.14285714284</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O39" s="33">
         <f t="shared" si="10"/>
-        <v>1712.5714285714287</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C40" s="19">
-        <v>46362</v>
+        <v>46332</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>68</v>
@@ -3874,7 +3934,7 @@
         <v>70</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H40" s="20" t="s">
         <v>74</v>
@@ -3882,28 +3942,28 @@
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
       <c r="K40" s="21">
-        <v>203796</v>
+        <v>187884</v>
       </c>
       <c r="M40" s="21">
         <f t="shared" si="9"/>
-        <v>21835.285714285714</v>
+        <v>20130.428571428572</v>
       </c>
       <c r="N40" s="27">
         <f t="shared" si="11"/>
-        <v>181960.71428571429</v>
+        <v>167753.57142857142</v>
       </c>
       <c r="O40" s="33">
         <f t="shared" si="10"/>
-        <v>1819.6071428571429</v>
+        <v>1677.5357142857142</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="12"/>
-        <v>8</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>91</v>
+        <v>6</v>
+      </c>
+      <c r="C41" s="19">
+        <v>46332</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>68</v>
@@ -3913,7 +3973,7 @@
         <v>70</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H41" s="20" t="s">
         <v>74</v>
@@ -3921,28 +3981,28 @@
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
       <c r="K41" s="21">
-        <v>190800</v>
+        <v>191808</v>
       </c>
       <c r="M41" s="21">
         <f t="shared" si="9"/>
-        <v>20442.857142857145</v>
+        <v>20550.857142857145</v>
       </c>
       <c r="N41" s="27">
         <f t="shared" si="11"/>
-        <v>170357.14285714284</v>
+        <v>171257.14285714284</v>
       </c>
       <c r="O41" s="33">
         <f t="shared" si="10"/>
-        <v>1703.5714285714287</v>
+        <v>1712.5714285714287</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>93</v>
+        <v>7</v>
+      </c>
+      <c r="C42" s="19">
+        <v>46362</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>68</v>
@@ -3952,7 +4012,7 @@
         <v>70</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H42" s="20" t="s">
         <v>74</v>
@@ -3960,28 +4020,28 @@
       <c r="I42" s="20"/>
       <c r="J42" s="20"/>
       <c r="K42" s="21">
-        <v>149328</v>
+        <v>203796</v>
       </c>
       <c r="M42" s="21">
         <f t="shared" si="9"/>
-        <v>15999.428571428571</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N42" s="27">
         <f t="shared" si="11"/>
-        <v>133328.57142857142</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O42" s="33">
         <f t="shared" si="10"/>
-        <v>1333.2857142857142</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>68</v>
@@ -3991,7 +4051,7 @@
         <v>70</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H43" s="20" t="s">
         <v>74</v>
@@ -3999,28 +4059,28 @@
       <c r="I43" s="20"/>
       <c r="J43" s="20"/>
       <c r="K43" s="21">
-        <v>163404</v>
+        <v>190800</v>
       </c>
       <c r="M43" s="21">
         <f t="shared" si="9"/>
-        <v>17507.571428571428</v>
+        <v>20442.857142857145</v>
       </c>
       <c r="N43" s="27">
         <f t="shared" si="11"/>
-        <v>145896.42857142858</v>
+        <v>170357.14285714284</v>
       </c>
       <c r="O43" s="33">
         <f t="shared" si="10"/>
-        <v>1458.9642857142858</v>
+        <v>1703.5714285714287</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>68</v>
@@ -4030,7 +4090,7 @@
         <v>70</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H44" s="20" t="s">
         <v>74</v>
@@ -4038,28 +4098,28 @@
       <c r="I44" s="20"/>
       <c r="J44" s="20"/>
       <c r="K44" s="21">
-        <v>191808</v>
+        <v>149328</v>
       </c>
       <c r="M44" s="21">
         <f t="shared" si="9"/>
-        <v>20550.857142857145</v>
+        <v>15999.428571428571</v>
       </c>
       <c r="N44" s="27">
         <f t="shared" si="11"/>
-        <v>171257.14285714284</v>
+        <v>133328.57142857142</v>
       </c>
       <c r="O44" s="33">
         <f t="shared" si="10"/>
-        <v>1712.5714285714287</v>
+        <v>1333.2857142857142</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>68</v>
@@ -4069,7 +4129,7 @@
         <v>70</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H45" s="20" t="s">
         <v>74</v>
@@ -4077,28 +4137,28 @@
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
       <c r="K45" s="21">
-        <v>204888</v>
+        <v>163404</v>
       </c>
       <c r="M45" s="21">
         <f t="shared" si="9"/>
-        <v>21952.285714285714</v>
+        <v>17507.571428571428</v>
       </c>
       <c r="N45" s="27">
         <f t="shared" si="11"/>
-        <v>182935.71428571429</v>
+        <v>145896.42857142858</v>
       </c>
       <c r="O45" s="33">
         <f t="shared" si="10"/>
-        <v>1829.3571428571429</v>
+        <v>1458.9642857142858</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="12"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D46" s="20" t="s">
         <v>68</v>
@@ -4108,7 +4168,7 @@
         <v>70</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H46" s="20" t="s">
         <v>74</v>
@@ -4116,28 +4176,28 @@
       <c r="I46" s="20"/>
       <c r="J46" s="20"/>
       <c r="K46" s="21">
-        <v>91656</v>
+        <v>191808</v>
       </c>
       <c r="M46" s="21">
         <f t="shared" si="9"/>
-        <v>9820.2857142857138</v>
+        <v>20550.857142857145</v>
       </c>
       <c r="N46" s="27">
         <f t="shared" si="11"/>
-        <v>81835.71428571429</v>
+        <v>171257.14285714284</v>
       </c>
       <c r="O46" s="33">
         <f t="shared" si="10"/>
-        <v>818.35714285714289</v>
+        <v>1712.5714285714287</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>68</v>
@@ -4147,7 +4207,7 @@
         <v>70</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H47" s="20" t="s">
         <v>74</v>
@@ -4155,28 +4215,28 @@
       <c r="I47" s="20"/>
       <c r="J47" s="20"/>
       <c r="K47" s="21">
-        <v>203796</v>
+        <v>204888</v>
       </c>
       <c r="M47" s="21">
         <f t="shared" si="9"/>
-        <v>21835.285714285714</v>
+        <v>21952.285714285714</v>
       </c>
       <c r="N47" s="27">
         <f t="shared" si="11"/>
-        <v>181960.71428571429</v>
+        <v>182935.71428571429</v>
       </c>
       <c r="O47" s="33">
         <f t="shared" si="10"/>
-        <v>1819.6071428571429</v>
+        <v>1829.3571428571429</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>68</v>
@@ -4186,7 +4246,7 @@
         <v>70</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H48" s="20" t="s">
         <v>74</v>
@@ -4194,28 +4254,28 @@
       <c r="I48" s="20"/>
       <c r="J48" s="20"/>
       <c r="K48" s="21">
-        <v>143856</v>
+        <v>91656</v>
       </c>
       <c r="M48" s="21">
         <f t="shared" si="9"/>
-        <v>15413.142857142855</v>
+        <v>9820.2857142857138</v>
       </c>
       <c r="N48" s="27">
         <f t="shared" si="11"/>
-        <v>128442.85714285714</v>
+        <v>81835.71428571429</v>
       </c>
       <c r="O48" s="33">
         <f t="shared" si="10"/>
-        <v>1284.4285714285713</v>
+        <v>818.35714285714289</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="12"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>68</v>
@@ -4225,7 +4285,7 @@
         <v>70</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H49" s="20" t="s">
         <v>74</v>
@@ -4233,28 +4293,29 @@
       <c r="I49" s="20"/>
       <c r="J49" s="20"/>
       <c r="K49" s="21">
-        <f>11988+10656+95904</f>
-        <v>118548</v>
+        <v>203796</v>
       </c>
       <c r="M49" s="21">
         <f t="shared" si="9"/>
-        <v>12701.571428571429</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N49" s="27">
         <f t="shared" si="11"/>
-        <v>105846.42857142857</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O49" s="33">
         <f t="shared" si="10"/>
-        <v>1058.4642857142858</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="12"/>
-        <v>17</v>
-      </c>
-      <c r="C50" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D50" s="20" t="s">
         <v>68</v>
       </c>
@@ -4262,32 +4323,38 @@
       <c r="F50" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G50" s="37"/>
+      <c r="G50" s="37" t="s">
+        <v>101</v>
+      </c>
       <c r="H50" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I50" s="20"/>
       <c r="J50" s="20"/>
-      <c r="K50" s="21"/>
+      <c r="K50" s="21">
+        <v>143856</v>
+      </c>
       <c r="M50" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15413.142857142855</v>
       </c>
       <c r="N50" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>128442.85714285714</v>
       </c>
       <c r="O50" s="33">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1284.4285714285713</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="12"/>
-        <v>18</v>
-      </c>
-      <c r="C51" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>112</v>
+      </c>
       <c r="D51" s="20" t="s">
         <v>68</v>
       </c>
@@ -4295,32 +4362,39 @@
       <c r="F51" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G51" s="37"/>
+      <c r="G51" s="37" t="s">
+        <v>113</v>
+      </c>
       <c r="H51" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
-      <c r="K51" s="21"/>
+      <c r="K51" s="21">
+        <f>11988+10656+95904</f>
+        <v>118548</v>
+      </c>
       <c r="M51" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>12701.571428571429</v>
       </c>
       <c r="N51" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>105846.42857142857</v>
       </c>
       <c r="O51" s="33">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1058.4642857142858</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="12"/>
-        <v>19</v>
-      </c>
-      <c r="C52" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D52" s="20" t="s">
         <v>68</v>
       </c>
@@ -4328,30 +4402,35 @@
       <c r="F52" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G52" s="37"/>
+      <c r="G52" s="37" t="s">
+        <v>121</v>
+      </c>
       <c r="H52" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
-      <c r="K52" s="21"/>
+      <c r="K52" s="21">
+        <f>7560+7560+10656+23976+5292+18144</f>
+        <v>73188</v>
+      </c>
       <c r="M52" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7841.5714285714275</v>
       </c>
       <c r="N52" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>65346.428571428572</v>
       </c>
       <c r="O52" s="33">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>653.46428571428567</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C53" s="19"/>
       <c r="D53" s="20" t="s">
@@ -4384,7 +4463,7 @@
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="12"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="20" t="s">
@@ -4401,226 +4480,214 @@
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
       <c r="K54" s="21"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
-      <c r="O54" s="33"/>
+      <c r="M54" s="21">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N54" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O54" s="33">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K55" s="44">
-        <f>SUM(K34:K54)</f>
-        <v>2727372</v>
-      </c>
-      <c r="L55" s="44">
-        <f ca="1">SUM(L34:L58)</f>
-        <v>0</v>
-      </c>
-      <c r="M55" s="44">
-        <f>SUM(M34:M54)</f>
-        <v>292218.42857142858</v>
-      </c>
-      <c r="N55" s="44">
-        <f>SUM(N34:N54)</f>
-        <v>2435153.5714285714</v>
-      </c>
-      <c r="O55" s="45">
-        <f>SUM(O34:O54)</f>
-        <v>24351.535714285714</v>
+      <c r="A55">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G55" s="37"/>
+      <c r="H55" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="21"/>
+      <c r="M55" s="21">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O55" s="33">
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O56" s="34"/>
-    </row>
-    <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C57" s="41" t="s">
+      <c r="A56">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G56" s="37"/>
+      <c r="H56" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="21"/>
+      <c r="M56" s="21"/>
+      <c r="N56" s="21"/>
+      <c r="O56" s="33"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K57" s="44">
+        <f>SUM(K36:K56)</f>
+        <v>2800560</v>
+      </c>
+      <c r="L57" s="44">
+        <f ca="1">SUM(L36:L60)</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="44">
+        <f>SUM(M36:M56)</f>
+        <v>300060</v>
+      </c>
+      <c r="N57" s="44">
+        <f>SUM(N36:N56)</f>
+        <v>2500500</v>
+      </c>
+      <c r="O57" s="45">
+        <f>SUM(O36:O56)</f>
+        <v>25005</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O58" s="34"/>
+    </row>
+    <row r="59" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C59" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="43" t="s">
+      <c r="D59" s="42"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="28"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="30"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="28"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="30"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9" t="s">
+      <c r="H61" s="9"/>
+      <c r="I61" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="J59" s="9" t="s">
+      <c r="J61" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="K59" s="10" t="s">
+      <c r="K61" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10" t="s">
+      <c r="M61" s="10"/>
+      <c r="N61" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="31"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="O61" s="31"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C62" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D62" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E62" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F62" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G62" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="H62" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I60" s="9" t="s">
+      <c r="I62" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="J60" s="9" t="s">
+      <c r="J62" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="K62" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M60" s="10" t="s">
+      <c r="M62" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N60" s="10" t="s">
+      <c r="N62" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O60" s="32">
+      <c r="O62" s="32">
         <v>2307</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>1</v>
-      </c>
-      <c r="C61" s="19">
-        <v>46028</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E61" s="12"/>
-      <c r="F61" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
-      <c r="K61" s="21">
-        <v>33804</v>
-      </c>
-      <c r="M61" s="21">
-        <f t="shared" ref="M61:M80" si="13">O61*12</f>
-        <v>3621.8571428571427</v>
-      </c>
-      <c r="N61" s="27">
-        <f>K61-M61</f>
-        <v>30182.142857142859</v>
-      </c>
-      <c r="O61" s="33">
-        <f t="shared" ref="O61:O80" si="14">K61/112</f>
-        <v>301.82142857142856</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <f>A61+1</f>
-        <v>2</v>
-      </c>
-      <c r="C62" s="19">
-        <v>46271</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G62" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="H62" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="21">
-        <v>11340</v>
-      </c>
-      <c r="M62" s="21">
-        <f t="shared" si="13"/>
-        <v>1215</v>
-      </c>
-      <c r="N62" s="27">
-        <f t="shared" ref="N62:N80" si="15">K62-M62</f>
-        <v>10125</v>
-      </c>
-      <c r="O62" s="33">
-        <f t="shared" si="14"/>
-        <v>101.25</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
-        <f t="shared" ref="A63:A81" si="16">A62+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C63" s="19">
-        <v>46332</v>
+        <v>46028</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E63" s="20"/>
+      <c r="E63" s="12"/>
       <c r="F63" s="20" t="s">
         <v>70</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H63" s="20" t="s">
         <v>74</v>
@@ -4628,28 +4695,28 @@
       <c r="I63" s="20"/>
       <c r="J63" s="20"/>
       <c r="K63" s="21">
-        <v>5670</v>
+        <v>33804</v>
       </c>
       <c r="M63" s="21">
-        <f t="shared" si="13"/>
-        <v>607.5</v>
+        <f t="shared" ref="M63:M82" si="13">O63*12</f>
+        <v>3621.8571428571427</v>
       </c>
       <c r="N63" s="27">
-        <f t="shared" si="15"/>
-        <v>5062.5</v>
+        <f>K63-M63</f>
+        <v>30182.142857142859</v>
       </c>
       <c r="O63" s="33">
-        <f t="shared" si="14"/>
-        <v>50.625</v>
+        <f t="shared" ref="O63:O82" si="14">K63/112</f>
+        <v>301.82142857142856</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <f t="shared" si="16"/>
-        <v>4</v>
+        <f>A63+1</f>
+        <v>2</v>
       </c>
       <c r="C64" s="19">
-        <v>46332</v>
+        <v>46271</v>
       </c>
       <c r="D64" s="20" t="s">
         <v>68</v>
@@ -4659,7 +4726,7 @@
         <v>70</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H64" s="20" t="s">
         <v>74</v>
@@ -4667,28 +4734,28 @@
       <c r="I64" s="20"/>
       <c r="J64" s="20"/>
       <c r="K64" s="21">
-        <v>5616</v>
+        <v>11340</v>
       </c>
       <c r="M64" s="21">
         <f t="shared" si="13"/>
-        <v>601.71428571428578</v>
+        <v>1215</v>
       </c>
       <c r="N64" s="27">
-        <f t="shared" si="15"/>
-        <v>5014.2857142857138</v>
+        <f t="shared" ref="N64:N82" si="15">K64-M64</f>
+        <v>10125</v>
       </c>
       <c r="O64" s="33">
         <f t="shared" si="14"/>
-        <v>50.142857142857146</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <f t="shared" si="16"/>
-        <v>5</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>93</v>
+        <f t="shared" ref="A65:A83" si="16">A64+1</f>
+        <v>3</v>
+      </c>
+      <c r="C65" s="19">
+        <v>46332</v>
       </c>
       <c r="D65" s="20" t="s">
         <v>68</v>
@@ -4698,7 +4765,7 @@
         <v>70</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H65" s="20" t="s">
         <v>74</v>
@@ -4706,28 +4773,28 @@
       <c r="I65" s="20"/>
       <c r="J65" s="20"/>
       <c r="K65" s="21">
-        <v>11286</v>
+        <v>5670</v>
       </c>
       <c r="M65" s="21">
         <f t="shared" si="13"/>
-        <v>1209.2142857142858</v>
+        <v>607.5</v>
       </c>
       <c r="N65" s="27">
         <f t="shared" si="15"/>
-        <v>10076.785714285714</v>
+        <v>5062.5</v>
       </c>
       <c r="O65" s="33">
         <f t="shared" si="14"/>
-        <v>100.76785714285714</v>
+        <v>50.625</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
         <f t="shared" si="16"/>
-        <v>6</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>77</v>
+        <v>4</v>
+      </c>
+      <c r="C66" s="19">
+        <v>46332</v>
       </c>
       <c r="D66" s="20" t="s">
         <v>68</v>
@@ -4737,7 +4804,7 @@
         <v>70</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H66" s="20" t="s">
         <v>74</v>
@@ -4763,10 +4830,10 @@
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
         <f t="shared" si="16"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D67" s="20" t="s">
         <v>68</v>
@@ -4776,7 +4843,7 @@
         <v>70</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H67" s="20" t="s">
         <v>74</v>
@@ -4784,28 +4851,28 @@
       <c r="I67" s="20"/>
       <c r="J67" s="20"/>
       <c r="K67" s="21">
-        <v>5616</v>
+        <v>11286</v>
       </c>
       <c r="M67" s="21">
         <f t="shared" si="13"/>
-        <v>601.71428571428578</v>
+        <v>1209.2142857142858</v>
       </c>
       <c r="N67" s="27">
         <f t="shared" si="15"/>
-        <v>5014.2857142857138</v>
+        <v>10076.785714285714</v>
       </c>
       <c r="O67" s="33">
         <f t="shared" si="14"/>
-        <v>50.142857142857146</v>
+        <v>100.76785714285714</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
         <f t="shared" si="16"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D68" s="20" t="s">
         <v>68</v>
@@ -4815,7 +4882,7 @@
         <v>70</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H68" s="20" t="s">
         <v>74</v>
@@ -4823,28 +4890,28 @@
       <c r="I68" s="20"/>
       <c r="J68" s="20"/>
       <c r="K68" s="21">
-        <v>5670</v>
+        <v>5616</v>
       </c>
       <c r="M68" s="21">
         <f t="shared" si="13"/>
-        <v>607.5</v>
+        <v>601.71428571428578</v>
       </c>
       <c r="N68" s="27">
         <f t="shared" si="15"/>
-        <v>5062.5</v>
+        <v>5014.2857142857138</v>
       </c>
       <c r="O68" s="33">
         <f t="shared" si="14"/>
-        <v>50.625</v>
+        <v>50.142857142857146</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
         <f t="shared" si="16"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D69" s="20" t="s">
         <v>68</v>
@@ -4854,7 +4921,7 @@
         <v>70</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H69" s="20" t="s">
         <v>74</v>
@@ -4880,9 +4947,11 @@
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
         <f t="shared" si="16"/>
-        <v>10</v>
-      </c>
-      <c r="C70" s="19"/>
+        <v>8</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>110</v>
+      </c>
       <c r="D70" s="20" t="s">
         <v>68</v>
       </c>
@@ -4890,32 +4959,38 @@
       <c r="F70" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G70" s="37"/>
+      <c r="G70" s="37" t="s">
+        <v>111</v>
+      </c>
       <c r="H70" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I70" s="20"/>
       <c r="J70" s="20"/>
-      <c r="K70" s="21"/>
+      <c r="K70" s="21">
+        <v>5670</v>
+      </c>
       <c r="M70" s="21">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>607.5</v>
       </c>
       <c r="N70" s="27">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>5062.5</v>
       </c>
       <c r="O70" s="33">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>50.625</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
         <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="C71" s="19"/>
+        <v>9</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>112</v>
+      </c>
       <c r="D71" s="20" t="s">
         <v>68</v>
       </c>
@@ -4923,32 +4998,38 @@
       <c r="F71" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G71" s="37"/>
+      <c r="G71" s="37" t="s">
+        <v>113</v>
+      </c>
       <c r="H71" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I71" s="20"/>
       <c r="J71" s="20"/>
-      <c r="K71" s="21"/>
+      <c r="K71" s="21">
+        <v>5616</v>
+      </c>
       <c r="M71" s="21">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>601.71428571428578</v>
       </c>
       <c r="N71" s="27">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>5014.2857142857138</v>
       </c>
       <c r="O71" s="33">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>50.142857142857146</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
         <f t="shared" si="16"/>
-        <v>12</v>
-      </c>
-      <c r="C72" s="19"/>
+        <v>10</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="D72" s="20" t="s">
         <v>68</v>
       </c>
@@ -4956,30 +5037,34 @@
       <c r="F72" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G72" s="37"/>
+      <c r="G72" s="37" t="s">
+        <v>113</v>
+      </c>
       <c r="H72" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I72" s="20"/>
       <c r="J72" s="20"/>
-      <c r="K72" s="21"/>
+      <c r="K72" s="21">
+        <v>5616</v>
+      </c>
       <c r="M72" s="21">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>601.71428571428578</v>
       </c>
       <c r="N72" s="27">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>5014.2857142857138</v>
       </c>
       <c r="O72" s="33">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>50.142857142857146</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
         <f t="shared" si="16"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C73" s="19"/>
       <c r="D73" s="20" t="s">
@@ -5012,7 +5097,7 @@
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="20" t="s">
@@ -5045,7 +5130,7 @@
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
         <f t="shared" si="16"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" s="19"/>
       <c r="D75" s="20" t="s">
@@ -5078,7 +5163,7 @@
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
         <f t="shared" si="16"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="20" t="s">
@@ -5111,7 +5196,7 @@
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C77" s="19"/>
       <c r="D77" s="20" t="s">
@@ -5144,7 +5229,7 @@
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="s">
@@ -5177,7 +5262,7 @@
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
         <f t="shared" si="16"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="20" t="s">
@@ -5210,7 +5295,7 @@
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
         <f t="shared" si="16"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="20" t="s">
@@ -5243,7 +5328,7 @@
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81">
         <f t="shared" si="16"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="20" t="s">
@@ -5260,234 +5345,214 @@
       <c r="I81" s="20"/>
       <c r="J81" s="20"/>
       <c r="K81" s="21"/>
-      <c r="M81" s="21"/>
-      <c r="N81" s="21"/>
-      <c r="O81" s="33"/>
+      <c r="M81" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N81" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O81" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K82" s="44">
-        <f>SUM(K61:K81)</f>
-        <v>90234</v>
-      </c>
-      <c r="L82" s="44">
-        <f ca="1">SUM(L61:L85)</f>
-        <v>0</v>
-      </c>
-      <c r="M82" s="44">
-        <f>SUM(M61:M81)</f>
-        <v>9667.9285714285743</v>
-      </c>
-      <c r="N82" s="44">
-        <f>SUM(N61:N81)</f>
-        <v>80566.071428571406</v>
-      </c>
-      <c r="O82" s="45">
-        <f>SUM(O61:O81)</f>
-        <v>805.66071428571422</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C84" s="41" t="s">
+      <c r="A82">
+        <f t="shared" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="C82" s="19"/>
+      <c r="D82" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G82" s="37"/>
+      <c r="H82" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="21"/>
+      <c r="M82" s="21">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N82" s="27">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O82" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="C83" s="19"/>
+      <c r="D83" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G83" s="37"/>
+      <c r="H83" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="21"/>
+      <c r="M83" s="21"/>
+      <c r="N83" s="21"/>
+      <c r="O83" s="33"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K84" s="44">
+        <f>SUM(K63:K83)</f>
+        <v>95850</v>
+      </c>
+      <c r="L84" s="44">
+        <f ca="1">SUM(L63:L87)</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="44">
+        <f>SUM(M63:M83)</f>
+        <v>10269.642857142861</v>
+      </c>
+      <c r="N84" s="44">
+        <f>SUM(N63:N83)</f>
+        <v>85580.357142857116</v>
+      </c>
+      <c r="O84" s="45">
+        <f>SUM(O63:O83)</f>
+        <v>855.80357142857133</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C86" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D84" s="42"/>
-      <c r="E84" s="42"/>
-      <c r="F84" s="43" t="s">
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-      <c r="M84" s="1"/>
-      <c r="N84" s="1"/>
-      <c r="O84" s="28"/>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
-      <c r="O85" s="30"/>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="9" t="s">
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="O86" s="28"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="M87" s="8"/>
+      <c r="N87" s="8"/>
+      <c r="O87" s="30"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H86" s="9"/>
-      <c r="I86" s="9" t="s">
+      <c r="H88" s="9"/>
+      <c r="I88" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="J86" s="9" t="s">
+      <c r="J88" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="M86" s="10" t="s">
+      <c r="M88" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="N86" s="10"/>
-      <c r="O86" s="10" t="s">
+      <c r="N88" s="10"/>
+      <c r="O88" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="P86" s="31"/>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="P88" s="31"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>73</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C89" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D89" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E89" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F87" s="9" t="s">
+      <c r="F89" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="G89" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H87" s="9" t="s">
+      <c r="H89" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I87" s="9" t="s">
+      <c r="I89" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="J87" s="9" t="s">
+      <c r="J89" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="K87" s="46" t="s">
+      <c r="K89" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="M87" s="10" t="s">
+      <c r="M89" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N87" s="10" t="s">
+      <c r="N89" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O87" s="10" t="s">
+      <c r="O89" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="P87" s="32">
+      <c r="P89" s="32">
         <v>2307</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>1</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E88" s="12"/>
-      <c r="F88" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G88" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="H88" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I88" s="20"/>
-      <c r="J88" s="20"/>
-      <c r="K88" s="21">
-        <v>1608</v>
-      </c>
-      <c r="L88" s="21"/>
-      <c r="M88" s="21">
-        <v>16488</v>
-      </c>
-      <c r="N88" s="21">
-        <f t="shared" ref="N88:N107" si="17">P88*12</f>
-        <v>1766.5714285714287</v>
-      </c>
-      <c r="O88" s="27">
-        <f t="shared" ref="O88:O107" si="18">M88-N88</f>
-        <v>14721.428571428571</v>
-      </c>
-      <c r="P88" s="33">
-        <f t="shared" ref="P88:P107" si="19">M88/112</f>
-        <v>147.21428571428572</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <f>A88+1</f>
-        <v>2</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D89" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G89" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="H89" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I89" s="20"/>
-      <c r="J89" s="20"/>
-      <c r="K89" s="21">
-        <v>1849</v>
-      </c>
-      <c r="L89" s="21"/>
-      <c r="M89" s="21">
-        <v>11328</v>
-      </c>
-      <c r="N89" s="21">
-        <f t="shared" si="17"/>
-        <v>1213.7142857142858</v>
-      </c>
-      <c r="O89" s="27">
-        <f t="shared" si="18"/>
-        <v>10114.285714285714</v>
-      </c>
-      <c r="P89" s="33">
-        <f t="shared" si="19"/>
-        <v>101.14285714285714</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90">
-        <f t="shared" ref="A90:A108" si="20">A89+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D90" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E90" s="20"/>
+      <c r="E90" s="12"/>
       <c r="F90" s="20" t="s">
         <v>70</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H90" s="20" t="s">
         <v>74</v>
@@ -5495,32 +5560,32 @@
       <c r="I90" s="20"/>
       <c r="J90" s="20"/>
       <c r="K90" s="21">
-        <v>1836</v>
+        <v>1608</v>
       </c>
       <c r="L90" s="21"/>
       <c r="M90" s="21">
-        <v>11016</v>
+        <v>16488</v>
       </c>
       <c r="N90" s="21">
-        <f t="shared" si="17"/>
-        <v>1180.2857142857142</v>
+        <f t="shared" ref="N90:N109" si="17">P90*12</f>
+        <v>1766.5714285714287</v>
       </c>
       <c r="O90" s="27">
-        <f t="shared" si="18"/>
-        <v>9835.7142857142862</v>
+        <f t="shared" ref="O90:O109" si="18">M90-N90</f>
+        <v>14721.428571428571</v>
       </c>
       <c r="P90" s="33">
-        <f t="shared" si="19"/>
-        <v>98.357142857142861</v>
+        <f t="shared" ref="P90:P109" si="19">M90/112</f>
+        <v>147.21428571428572</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91">
-        <f t="shared" si="20"/>
-        <v>4</v>
+        <f>A90+1</f>
+        <v>2</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>68</v>
@@ -5530,7 +5595,7 @@
         <v>70</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H91" s="20" t="s">
         <v>74</v>
@@ -5538,32 +5603,32 @@
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="21">
-        <v>1709</v>
+        <v>1849</v>
       </c>
       <c r="L91" s="21"/>
       <c r="M91" s="21">
-        <v>13800</v>
+        <v>11328</v>
       </c>
       <c r="N91" s="21">
         <f t="shared" si="17"/>
-        <v>1478.5714285714284</v>
+        <v>1213.7142857142858</v>
       </c>
       <c r="O91" s="27">
         <f t="shared" si="18"/>
-        <v>12321.428571428572</v>
+        <v>10114.285714285714</v>
       </c>
       <c r="P91" s="33">
         <f t="shared" si="19"/>
-        <v>123.21428571428571</v>
+        <v>101.14285714285714</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92">
-        <f t="shared" si="20"/>
-        <v>5</v>
+        <f t="shared" ref="A92:A110" si="20">A91+1</f>
+        <v>3</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D92" s="20" t="s">
         <v>68</v>
@@ -5573,7 +5638,7 @@
         <v>70</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H92" s="20" t="s">
         <v>74</v>
@@ -5603,10 +5668,10 @@
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>68</v>
@@ -5616,7 +5681,7 @@
         <v>70</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H93" s="20" t="s">
         <v>74</v>
@@ -5624,31 +5689,33 @@
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="21">
-        <v>1836</v>
+        <v>1709</v>
       </c>
       <c r="L93" s="21"/>
       <c r="M93" s="21">
-        <v>11016</v>
+        <v>13800</v>
       </c>
       <c r="N93" s="21">
         <f t="shared" si="17"/>
-        <v>1180.2857142857142</v>
+        <v>1478.5714285714284</v>
       </c>
       <c r="O93" s="27">
         <f t="shared" si="18"/>
-        <v>9835.7142857142862</v>
+        <v>12321.428571428572</v>
       </c>
       <c r="P93" s="33">
         <f t="shared" si="19"/>
-        <v>98.357142857142861</v>
+        <v>123.21428571428571</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94">
         <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="C94" s="19"/>
+        <v>5</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D94" s="20" t="s">
         <v>68</v>
       </c>
@@ -5656,34 +5723,42 @@
       <c r="F94" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G94" s="37"/>
+      <c r="G94" s="37" t="s">
+        <v>108</v>
+      </c>
       <c r="H94" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
-      <c r="K94" s="21"/>
+      <c r="K94" s="21">
+        <v>1836</v>
+      </c>
       <c r="L94" s="21"/>
-      <c r="M94" s="21"/>
+      <c r="M94" s="21">
+        <v>11016</v>
+      </c>
       <c r="N94" s="21">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1180.2857142857142</v>
       </c>
       <c r="O94" s="27">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>9835.7142857142862</v>
       </c>
       <c r="P94" s="33">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>98.357142857142861</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95">
         <f t="shared" si="20"/>
-        <v>8</v>
-      </c>
-      <c r="C95" s="19"/>
+        <v>6</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D95" s="20" t="s">
         <v>68</v>
       </c>
@@ -5691,32 +5766,38 @@
       <c r="F95" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G95" s="37"/>
+      <c r="G95" s="37" t="s">
+        <v>109</v>
+      </c>
       <c r="H95" s="20" t="s">
         <v>74</v>
       </c>
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
-      <c r="K95" s="21"/>
+      <c r="K95" s="21">
+        <v>1836</v>
+      </c>
       <c r="L95" s="21"/>
-      <c r="M95" s="21"/>
+      <c r="M95" s="21">
+        <v>11016</v>
+      </c>
       <c r="N95" s="21">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1180.2857142857142</v>
       </c>
       <c r="O95" s="27">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>9835.7142857142862</v>
       </c>
       <c r="P95" s="33">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>98.357142857142861</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
         <f t="shared" si="20"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C96" s="19"/>
       <c r="D96" s="20" t="s">
@@ -5751,7 +5832,7 @@
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <f t="shared" si="20"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C97" s="19"/>
       <c r="D97" s="20" t="s">
@@ -5786,7 +5867,7 @@
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <f t="shared" si="20"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C98" s="19"/>
       <c r="D98" s="20" t="s">
@@ -5821,7 +5902,7 @@
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <f t="shared" si="20"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C99" s="19"/>
       <c r="D99" s="20" t="s">
@@ -5856,7 +5937,7 @@
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <f t="shared" si="20"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C100" s="19"/>
       <c r="D100" s="20" t="s">
@@ -5891,7 +5972,7 @@
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <f t="shared" si="20"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C101" s="19"/>
       <c r="D101" s="20" t="s">
@@ -5926,7 +6007,7 @@
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102">
         <f t="shared" si="20"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C102" s="19"/>
       <c r="D102" s="20" t="s">
@@ -5961,7 +6042,7 @@
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103">
         <f t="shared" si="20"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C103" s="19"/>
       <c r="D103" s="20" t="s">
@@ -5996,7 +6077,7 @@
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104">
         <f t="shared" si="20"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C104" s="19"/>
       <c r="D104" s="20" t="s">
@@ -6031,7 +6112,7 @@
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105">
         <f t="shared" si="20"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C105" s="19"/>
       <c r="D105" s="20" t="s">
@@ -6066,7 +6147,7 @@
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106">
         <f t="shared" si="20"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C106" s="19"/>
       <c r="D106" s="20" t="s">
@@ -6101,7 +6182,7 @@
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107">
         <f t="shared" si="20"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C107" s="19"/>
       <c r="D107" s="20" t="s">
@@ -6136,7 +6217,7 @@
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108">
         <f t="shared" si="20"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C108" s="19"/>
       <c r="D108" s="20" t="s">
@@ -6155,33 +6236,103 @@
       <c r="K108" s="21"/>
       <c r="L108" s="21"/>
       <c r="M108" s="21"/>
-      <c r="N108" s="21"/>
-      <c r="O108" s="21"/>
-      <c r="P108" s="33"/>
+      <c r="N108" s="21">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O108" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P108" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K109" s="44">
-        <f>SUM(K88:K108)</f>
+      <c r="A109">
+        <f t="shared" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="C109" s="19"/>
+      <c r="D109" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G109" s="37"/>
+      <c r="H109" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I109" s="20"/>
+      <c r="J109" s="20"/>
+      <c r="K109" s="21"/>
+      <c r="L109" s="21"/>
+      <c r="M109" s="21"/>
+      <c r="N109" s="21">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O109" s="27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P109" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <f t="shared" si="20"/>
+        <v>21</v>
+      </c>
+      <c r="C110" s="19"/>
+      <c r="D110" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E110" s="20"/>
+      <c r="F110" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G110" s="37"/>
+      <c r="H110" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I110" s="20"/>
+      <c r="J110" s="20"/>
+      <c r="K110" s="21"/>
+      <c r="L110" s="21"/>
+      <c r="M110" s="21"/>
+      <c r="N110" s="21"/>
+      <c r="O110" s="21"/>
+      <c r="P110" s="33"/>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K111" s="44">
+        <f>SUM(K90:K110)</f>
         <v>10674</v>
       </c>
-      <c r="L109" s="44">
-        <f ca="1">SUM(L88:L112)</f>
-        <v>0</v>
-      </c>
-      <c r="M109" s="44">
-        <f>SUM(M88:M108)</f>
+      <c r="L111" s="44">
+        <f ca="1">SUM(L90:L114)</f>
+        <v>0</v>
+      </c>
+      <c r="M111" s="44">
+        <f>SUM(M90:M110)</f>
         <v>74664</v>
       </c>
-      <c r="N109" s="44">
-        <f>SUM(N88:N108)</f>
+      <c r="N111" s="44">
+        <f>SUM(N90:N110)</f>
         <v>7999.7142857142862</v>
       </c>
-      <c r="O109" s="45">
-        <f>SUM(O88:O108)</f>
+      <c r="O111" s="45">
+        <f>SUM(O90:O110)</f>
         <v>66664.28571428571</v>
       </c>
-      <c r="P109" s="45">
-        <f>SUM(P88:P108)</f>
+      <c r="P111" s="45">
+        <f>SUM(P90:P110)</f>
         <v>666.64285714285722</v>
       </c>
     </row>
